--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4CDD46-B5C7-4F16-B606-47796C1D7A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B2F6D7-9E3E-47A6-936C-2B2A5A7A3F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="165" windowWidth="18420" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="975" yWindow="495" windowWidth="24255" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
     <sheet name="Legend" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="102">
   <si>
     <t>active</t>
   </si>
@@ -60,9 +60,6 @@
     <t>dom_count_min</t>
   </si>
   <si>
-    <t>dom_count_frac</t>
-  </si>
-  <si>
     <t>tickers_per_group</t>
   </si>
   <si>
@@ -117,15 +114,15 @@
     <t>Stamdata.Sector2</t>
   </si>
   <si>
+    <t>x</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
     <t>Stamdata.Zone .and. Stamdata.GICS</t>
   </si>
   <si>
-    <t>#ALL</t>
-  </si>
-  <si>
     <t>fr_best</t>
   </si>
   <si>
@@ -279,12 +276,6 @@
     <t>Absolute floor on qualifying tickers a group needs to dominate.</t>
   </si>
   <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>Qualifying-ticker threshold as a fraction of the group's own size. threshold = max(dom_count_min, ceil(dom_count_frac * group_size)). Set to 0 to reproduce strategy_grp v1's fixed absolute count.</t>
-  </si>
-  <si>
     <t>Top candidates drawn from EACH dominating group into the pooled test-set (per level: A=3, B=4, C=5 is SM's proposal).</t>
   </si>
   <si>
@@ -336,7 +327,7 @@
     <t>Candidate pool (by label, comma-separated) for selection-skill scoring. Blank = every other active D-purpose row.</t>
   </si>
   <si>
-    <t>x</t>
+    <t>per1d,future_per5d,future_per10d,future_per20d</t>
   </si>
 </sst>
 </file>
@@ -726,15 +717,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" customWidth="1"/>
-    <col min="6" max="23" width="18" customWidth="1"/>
+    <col min="1" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="55.42578125" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +765,7 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
@@ -789,7 +780,7 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="5" t="s">
@@ -798,31 +789,28 @@
       <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
       </c>
       <c r="K2">
         <v>0.1</v>
@@ -831,48 +819,48 @@
         <v>10</v>
       </c>
       <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>5</v>
+      </c>
+      <c r="S2">
+        <v>20</v>
+      </c>
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>5</v>
-      </c>
-      <c r="T2">
-        <v>20</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
       </c>
       <c r="K3">
         <v>0.1</v>
@@ -881,51 +869,51 @@
         <v>5</v>
       </c>
       <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>5</v>
+      </c>
+      <c r="S3">
+        <v>20</v>
+      </c>
+      <c r="T3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>5</v>
-      </c>
-      <c r="T3">
-        <v>20</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
         <v>32</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>27</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
       </c>
       <c r="K4">
         <v>0.1</v>
@@ -934,107 +922,113 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>0.15</v>
-      </c>
-      <c r="N4">
         <v>5</v>
       </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
       <c r="P4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4">
-        <v>20</v>
-      </c>
-      <c r="U4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
       </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
         <v>26</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
       </c>
       <c r="K5">
         <v>0.1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>0.15</v>
-      </c>
-      <c r="N5">
         <v>5</v>
       </c>
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
       <c r="P5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5">
-        <v>20</v>
-      </c>
-      <c r="U5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U5" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>26</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
       </c>
       <c r="K6">
         <v>0.1</v>
@@ -1043,57 +1037,57 @@
         <v>10</v>
       </c>
       <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+      <c r="T6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="P6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>5</v>
-      </c>
-      <c r="T6">
-        <v>20</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="W6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U6" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>26</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>27</v>
-      </c>
-      <c r="J7" t="s">
-        <v>28</v>
       </c>
       <c r="K7">
         <v>0.1</v>
@@ -1102,90 +1096,31 @@
         <v>10</v>
       </c>
       <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7">
+        <v>-1</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <v>20</v>
+      </c>
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="P7" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>37</v>
-      </c>
-      <c r="S7">
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <v>20</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="W7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8">
-        <v>0.1</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>5</v>
-      </c>
-      <c r="P8" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8">
-        <v>-1</v>
-      </c>
-      <c r="S8">
-        <v>5</v>
-      </c>
-      <c r="T8">
-        <v>20</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="W8" t="s">
-        <v>35</v>
+      <c r="U7" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1205,68 +1140,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>315</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>63</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1289,22 +1224,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1312,16 +1247,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>58</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,19 +1264,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
       <c r="E3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,13 +1284,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,13 +1298,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1380,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1394,16 +1329,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1414,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1428,13 +1363,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,13 +1380,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1462,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
         <v>78</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1479,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1496,16 +1431,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1513,30 +1448,27 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1547,10 +1479,13 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,16 +1496,16 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1578,16 +1513,16 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1595,13 +1530,13 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1609,12 +1544,15 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
         <v>93</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1629,16 +1567,13 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>95</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1649,7 +1584,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
         <v>98</v>
@@ -1658,35 +1593,18 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B2F6D7-9E3E-47A6-936C-2B2A5A7A3F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611E44D2-EB13-49F1-8FB8-1536C660A58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="495" windowWidth="24255" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3195" yWindow="2340" windowWidth="25335" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="109">
   <si>
     <t>active</t>
   </si>
@@ -328,6 +328,27 @@
   </si>
   <si>
     <t>per1d,future_per5d,future_per10d,future_per20d</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>From strategy_grp</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>small_wins</t>
+  </si>
+  <si>
+    <t>Calm</t>
+  </si>
+  <si>
+    <t>Agressive</t>
+  </si>
+  <si>
+    <t>future_minaggr20d</t>
   </si>
 </sst>
 </file>
@@ -717,10 +738,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="20" width="18" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="55.42578125" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
@@ -819,16 +848,16 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
         <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R2">
         <v>5</v>
@@ -869,16 +898,16 @@
         <v>5</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O3" t="s">
         <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R3">
         <v>5</v>
@@ -922,16 +951,16 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -947,9 +976,6 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
       <c r="B5" t="s">
         <v>31</v>
       </c>
@@ -978,16 +1004,16 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O5" t="s">
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1006,9 +1032,6 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
@@ -1037,13 +1060,13 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
         <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
@@ -1065,9 +1088,6 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -1096,13 +1116,13 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" t="s">
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1121,6 +1141,174 @@
       </c>
       <c r="V7" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>0.1</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="O8" t="s">
+        <v>75</v>
+      </c>
+      <c r="P8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8">
+        <v>-1</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>0.1</v>
+      </c>
+      <c r="L9">
+        <v>10</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q9">
+        <v>-1</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10">
+        <v>0.1</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q10">
+        <v>-1</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+      <c r="S10">
+        <v>20</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611E44D2-EB13-49F1-8FB8-1536C660A58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90273771-ADB9-47C7-B847-E9E6E010309D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="2340" windowWidth="25335" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="645" windowWidth="25335" windowHeight="9855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="110">
   <si>
     <t>active</t>
   </si>
@@ -349,13 +349,16 @@
   </si>
   <si>
     <t>future_minaggr20d</t>
+  </si>
+  <si>
+    <t>conf_Sector2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +370,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -412,10 +421,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDotDot">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -424,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -435,6 +453,9 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -857,7 +878,7 @@
         <v>105</v>
       </c>
       <c r="Q2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>5</v>
@@ -907,7 +928,7 @@
         <v>105</v>
       </c>
       <c r="Q3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>5</v>
@@ -960,7 +981,7 @@
         <v>105</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -1013,7 +1034,7 @@
         <v>105</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1289,14 +1310,14 @@
       <c r="M10">
         <v>3</v>
       </c>
-      <c r="O10" t="s">
-        <v>28</v>
+      <c r="O10" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="P10" t="s">
         <v>105</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R10">
         <v>5</v>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AD1477-BFB0-43D2-96E6-26118D0ADD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1190B29A-56A1-40F1-94DA-0AF12E0EA7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="420" windowWidth="28305" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20145" yWindow="2115" windowWidth="27345" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="128">
   <si>
     <t>active</t>
   </si>
@@ -117,15 +117,9 @@
     <t>small_wins</t>
   </si>
   <si>
-    <t>per1d,future_per5d,future_per10d,future_per20d</t>
-  </si>
-  <si>
     <t>spr100d</t>
   </si>
   <si>
-    <t>conf_GICS</t>
-  </si>
-  <si>
     <t>Stamdata.Sector2</t>
   </si>
   <si>
@@ -373,6 +367,45 @@
   </si>
   <si>
     <t>Candidate pool (by label, comma-separated) for selection-skill scoring. Blank = every other active D-purpose row.</t>
+  </si>
+  <si>
+    <t>per1d</t>
+  </si>
+  <si>
+    <t>Stamdata.GICS .and. Stamdata.Zone='NY'</t>
+  </si>
+  <si>
+    <t>Longi.per1d&gt;0</t>
+  </si>
+  <si>
+    <t>4 (-1) NY</t>
+  </si>
+  <si>
+    <t>4 (-1) NY post-filter</t>
+  </si>
+  <si>
+    <t>5 (-1) NY</t>
+  </si>
+  <si>
+    <t>5 (-1) NY post-filter</t>
+  </si>
+  <si>
+    <t>Stamdata.Sector2 .and. Stamdata.Zone='NY'</t>
+  </si>
+  <si>
+    <t>11 (-1) NY</t>
+  </si>
+  <si>
+    <t>12 (-1) NY</t>
+  </si>
+  <si>
+    <t>per1d,spr100d</t>
+  </si>
+  <si>
+    <t>Longi.spr100d&lt;20</t>
+  </si>
+  <si>
+    <t>Longi.spr100d&lt;50</t>
   </si>
 </sst>
 </file>
@@ -391,16 +424,16 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -448,6 +481,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -461,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -474,7 +513,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,10 +818,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="20" width="18" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="39.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="48.42578125" customWidth="1"/>
     <col min="22" max="23" width="18" customWidth="1"/>
   </cols>
@@ -822,7 +871,7 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
@@ -837,7 +886,7 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
@@ -860,6 +909,9 @@
       <c r="B2" t="s">
         <v>24</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="E2" t="s">
         <v>25</v>
       </c>
@@ -900,122 +952,117 @@
         <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="V2">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="R3">
+        <v>5</v>
+      </c>
+      <c r="S3">
+        <v>20</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>115</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="str">
+        <f>C3 &amp; " + stop "&amp;V4</f>
+        <v>2 + stop -20</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="9">
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4">
         <v>0.1</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L4">
         <v>10</v>
       </c>
-      <c r="M3" s="9">
-        <v>3</v>
-      </c>
-      <c r="O3" s="9" t="s">
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P4" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R3" s="9">
-        <v>5</v>
-      </c>
-      <c r="S3" s="9">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
         <v>20</v>
       </c>
-      <c r="T3" s="9">
-        <v>0</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="L4" s="9">
-        <v>10</v>
-      </c>
-      <c r="M4" s="9">
-        <v>3</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>-1</v>
-      </c>
-      <c r="R4" s="9">
-        <v>5</v>
-      </c>
-      <c r="S4" s="9">
-        <v>20</v>
-      </c>
-      <c r="T4" s="9">
-        <v>0</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="9">
-        <v>0</v>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>115</v>
+      </c>
+      <c r="V4">
+        <v>-20</v>
       </c>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1025,12 +1072,11 @@
       <c r="B5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="9" t="str">
-        <f>C4 &amp; " + stop "&amp;V5</f>
-        <v>2 + stop -20</v>
+      <c r="C5" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>26</v>
@@ -1048,10 +1094,11 @@
         <v>10</v>
       </c>
       <c r="M5" s="9">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N5" s="10"/>
       <c r="O5" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P5" s="9" t="s">
         <v>30</v>
@@ -1069,10 +1116,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" s="9">
-        <v>-20</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1082,11 +1126,11 @@
       <c r="B6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9">
-        <v>3</v>
+      <c r="C6" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>26</v>
@@ -1104,10 +1148,13 @@
         <v>10</v>
       </c>
       <c r="M6" s="9">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>126</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P6" s="9" t="s">
         <v>30</v>
@@ -1125,10 +1172,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" s="9">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1138,12 +1182,11 @@
       <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="9" t="str">
-        <f>C6 &amp; " + stop "&amp;V7</f>
-        <v>3 + stop -20</v>
+      <c r="C7" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -1161,10 +1204,13 @@
         <v>10</v>
       </c>
       <c r="M7" s="9">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P7" s="9" t="s">
         <v>30</v>
@@ -1182,433 +1228,339 @@
         <v>0</v>
       </c>
       <c r="U7" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L8" s="9">
+        <v>10</v>
+      </c>
+      <c r="M8" s="9">
+        <v>3</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="V7" s="9">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="P8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R8" s="9">
+        <v>5</v>
+      </c>
+      <c r="S8" s="9">
+        <v>20</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K8">
+      <c r="K9" s="9">
         <v>0.1</v>
       </c>
-      <c r="L8">
+      <c r="L9" s="9">
         <v>10</v>
       </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-      <c r="O8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="M9" s="9">
+        <v>3</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1</v>
+      </c>
+      <c r="R9" s="9">
+        <v>5</v>
+      </c>
+      <c r="S9" s="9">
+        <v>20</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Q8">
+      <c r="K10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9">
+        <v>10</v>
+      </c>
+      <c r="M10" s="9">
+        <v>3</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="9">
         <v>1</v>
       </c>
-      <c r="R8">
-        <v>5</v>
-      </c>
-      <c r="S8">
+      <c r="R10" s="9">
+        <v>5</v>
+      </c>
+      <c r="S10" s="9">
         <v>20</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="L12" s="11">
+        <v>5</v>
+      </c>
+      <c r="M12" s="11">
+        <v>3</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11">
+        <v>5</v>
+      </c>
+      <c r="S12" s="11">
+        <v>20</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="V12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="11">
+        <v>3</v>
+      </c>
+      <c r="M13" s="11">
+        <v>3</v>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="P13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="R13" s="11">
+        <v>5</v>
+      </c>
+      <c r="S13" s="11">
+        <v>20</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C14" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K9">
+      <c r="K14" s="11">
         <v>0.1</v>
       </c>
-      <c r="L9">
-        <v>5</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
-      </c>
-      <c r="O9" t="s">
-        <v>29</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="L14" s="11">
+        <v>3</v>
+      </c>
+      <c r="M14" s="11">
+        <v>3</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="Q9">
+      <c r="Q14" s="11">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>5</v>
-      </c>
-      <c r="S9">
+      <c r="R14" s="11">
+        <v>5</v>
+      </c>
+      <c r="S14" s="11">
         <v>20</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10">
-        <v>0.1</v>
-      </c>
-      <c r="L10">
-        <v>5</v>
-      </c>
-      <c r="M10">
-        <v>3</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>5</v>
-      </c>
-      <c r="S10">
-        <v>20</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11">
-        <v>0.1</v>
-      </c>
-      <c r="L11">
-        <v>5</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-      <c r="O11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>5</v>
-      </c>
-      <c r="S11">
-        <v>20</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12">
-        <v>0.1</v>
-      </c>
-      <c r="L12">
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <v>3</v>
-      </c>
-      <c r="O12" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>5</v>
-      </c>
-      <c r="S12">
-        <v>20</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13">
-        <v>0.1</v>
-      </c>
-      <c r="L13">
-        <v>10</v>
-      </c>
-      <c r="M13">
-        <v>3</v>
-      </c>
-      <c r="O13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P13" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>5</v>
-      </c>
-      <c r="S13">
-        <v>20</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>31</v>
-      </c>
-      <c r="W13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14">
-        <v>0.1</v>
-      </c>
-      <c r="L14">
-        <v>10</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
-      </c>
-      <c r="O14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>5</v>
-      </c>
-      <c r="S14">
-        <v>20</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14" t="s">
-        <v>31</v>
-      </c>
-      <c r="W14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15">
-        <v>0.1</v>
-      </c>
-      <c r="L15">
-        <v>10</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="O15" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q15">
-        <v>-1</v>
-      </c>
-      <c r="R15">
-        <v>5</v>
-      </c>
-      <c r="S15">
-        <v>20</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
-        <v>31</v>
-      </c>
-      <c r="W15" t="s">
-        <v>39</v>
-      </c>
+      <c r="T14" s="11">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>24</v>
       </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
         <v>27</v>
@@ -1620,10 +1572,10 @@
         <v>0.1</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O16" t="s">
         <v>29</v>
@@ -1632,7 +1584,7 @@
         <v>30</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -1644,24 +1596,21 @@
         <v>0</v>
       </c>
       <c r="U16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="V16">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>24</v>
       </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
         <v>27</v>
@@ -1673,19 +1622,19 @@
         <v>0.1</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P17" t="s">
         <v>30</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <v>5</v>
@@ -1697,21 +1646,15 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>43</v>
-      </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -1732,10 +1675,10 @@
         <v>3</v>
       </c>
       <c r="O18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1750,7 +1693,381 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19">
+        <v>0.1</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="O19" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>5</v>
+      </c>
+      <c r="S19">
+        <v>20</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20">
+        <v>0.1</v>
+      </c>
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+      <c r="S20">
+        <v>20</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="s">
+        <v>115</v>
+      </c>
+      <c r="W20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21">
+        <v>0.1</v>
+      </c>
+      <c r="L21">
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+      <c r="S21">
+        <v>20</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" t="s">
+        <v>115</v>
+      </c>
+      <c r="W21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22">
+        <v>0.1</v>
+      </c>
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22">
+        <v>-1</v>
+      </c>
+      <c r="R22">
+        <v>5</v>
+      </c>
+      <c r="S22">
+        <v>20</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22" t="s">
+        <v>115</v>
+      </c>
+      <c r="W22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23">
+        <v>0.1</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="O23" t="s">
+        <v>29</v>
+      </c>
+      <c r="P23" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23">
+        <v>-1</v>
+      </c>
+      <c r="R23">
+        <v>5</v>
+      </c>
+      <c r="S23">
+        <v>20</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24">
+        <v>0.1</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="O24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q24">
+        <v>-1</v>
+      </c>
+      <c r="R24">
+        <v>5</v>
+      </c>
+      <c r="S24">
+        <v>20</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
         <v>45</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25">
+        <v>0.1</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P25" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>5</v>
+      </c>
+      <c r="S25">
+        <v>20</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1771,90 +2088,90 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>315</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>63</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1877,22 +2194,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1900,16 +2217,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1917,19 +2234,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,13 +2254,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1951,13 +2268,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1968,10 +2285,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1982,16 +2299,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2002,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2016,13 +2333,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2033,13 +2350,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,13 +2367,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2067,13 +2384,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,13 +2401,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2101,13 +2418,13 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2118,10 +2435,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,13 +2449,13 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2149,13 +2466,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2169,10 +2486,10 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2200,16 +2517,16 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2220,13 +2537,13 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2237,13 +2554,13 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2254,13 +2571,13 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2271,10 +2588,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -495,1814 +495,1512 @@
     <col width="18" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>group_expression</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>persistence_window</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>persistence_frac</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>dominance_attribute</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>dominance_direction</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>dominance_decile</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>dom_count_min</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>tickers_per_group</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>post_filter</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>priority_attribute</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>priority_direction</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>from_rank</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>focusset_size</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>no_go_gspc_rsi</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>informational_attributes</t>
+        </is>
+      </c>
+      <c r="W1" s="6" t="inlineStr">
+        <is>
+          <t>wf_group</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>group_expression</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>persistence_window</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>persistence_frac</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>dominance_attribute</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>dominance_direction</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>dominance_decile</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>dom_count_min</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>tickers_per_group</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>post_filter</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>priority_attribute</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>priority_direction</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>from_rank</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>focusset_size</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>stop_loss</t>
-        </is>
-      </c>
-      <c r="S1" s="5" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="T1" s="5" t="inlineStr">
-        <is>
-          <t>no_go_gspc_rsi</t>
-        </is>
-      </c>
-      <c r="U1" s="5" t="inlineStr">
-        <is>
-          <t>informational_attributes</t>
-        </is>
-      </c>
-      <c r="V1" s="6" t="inlineStr">
-        <is>
-          <t>wf_group</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GICS-beta3m(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bedst</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stamdata.GICS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>beta3m</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>beta3m</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>20</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GICS-PdivMA20(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>God</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stamdata.GICS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PdivMA20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>beta3m</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GICS-rank(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>God</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stamdata.GICS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>small_wins</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>beta3m</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GICS-sh3m(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>God</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stamdata.GICS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sh3m</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>beta3m</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Fkgr-beta3m(beta3m 1)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>0.1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L6" t="n">
         <v>10</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R6" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>20</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+    <row r="7">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Fkgr-median_30d(beta3m 1)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>median_30d</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>small_wins</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K7" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R7" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>20</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+    <row r="8">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Fkgr-PdivMA20(beta3m 1)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>PdivMA20</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>0.1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>20</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
+    <row r="9">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Fkgr-per20d(beta3m 1)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>per20d</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>0.1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L9" t="n">
         <v>10</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M9" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R9" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>20</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="10">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Fkgr-quot1020(beta3m 1)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>quot1020</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>0.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L10" t="n">
         <v>10</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M10" t="n">
         <v>4</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>20</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
+    <row r="11">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Fkgr-quot2050(beta3m 1)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>quot2050</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>0.1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L11" t="n">
         <v>10</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R11" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>20</v>
       </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
+    <row r="12">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Fkgr-rank(beta3m 1)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>small_wins</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K12" t="n">
         <v>0.1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R12" t="n">
         <v>3</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>20</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
+    <row r="13">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Fkgr-rsi(beta3m 1)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>rsi</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>0.1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L13" t="n">
         <v>10</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M13" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R13" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>20</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
+    <row r="14">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Fkgr-sh3m(beta3m 1)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>sh3m</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>0.1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L14" t="n">
         <v>10</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M14" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R14" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>20</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
+    <row r="15">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Fkgr-spr100d(beta3m 1)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>spr100d</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>small_wins</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K15" t="n">
         <v>0.1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L15" t="n">
         <v>10</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M15" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R15" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>20</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="16">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Fkgr-vola20d(beta3m 1)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Stamdata.Fkgrade</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>vola20d</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>0.1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L16" t="n">
         <v>10</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M16" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R16" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>20</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GICS-beta3m(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GICS-rsi(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Stamdata.GICS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>rsi</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GICS-spr100d(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Stamdata.GICS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>spr100d</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>small_wins</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>0.1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L18" t="n">
         <v>10</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M18" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R18" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GICS-beta3m(beta3m 1) Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ZONE-quot2050(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Stamdata.ZONE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>quot2050</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>20</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>rank, rsi, vola20d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ZONE-sh3m(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Stamdata.ZONE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>sh3m</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>0.1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L20" t="n">
         <v>10</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M20" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>20</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GICS-PdivMA20(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZONE-spr100d(beta3m 1)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Stamdata.ZONE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>PdivMA20</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>spr100d</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>small_wins</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>0.1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L21" t="n">
         <v>10</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M21" t="n">
         <v>4</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>beta3m</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>big_wins</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>20</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>GICS-PdivMA20(beta3m 1) Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>PdivMA20</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>20</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>GICS-rank(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>small_wins</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>20</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GICS-rank(beta3m 1) Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>small_wins</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>20</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GICS-rsi(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>rsi</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>20</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>GICS-sh3m(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>sh3m</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>20</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GICS-sh3m(beta3m 1) Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>sh3m</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Longi.rank&lt;1000</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>20</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>GICS-spr100d(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stamdata.GICS</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>spr100d</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>small_wins</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ZONE-quot2050(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Stamdata.ZONE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>quot2050</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>20</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ZONE-sh3m(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Stamdata.ZONE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>sh3m</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>20</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>rank, rsi, vola20d</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ZONE-spr100d(beta3m 1)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stamdata.ZONE</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>spr100d</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>small_wins</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>beta3m</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>big_wins</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>rank, rsi, vola20d</t>
         </is>
@@ -2462,7 +2160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2508,7 +2206,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2529,14 +2227,14 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>x / blank — run this row this tick.</t>
+          <t>x / blank — include this row in a development tick (steps 0-4, compare_strategies_&lt;date&gt;.xlsx). Independent of P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2546,21 +2244,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Sheet/column header on the output board. Blank = auto-derived.</t>
+          <t>x / blank — include this row in a --production run (StrategicStocks, Drive-published). Independent of D — mark both to run in both modes.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>label</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2577,66 +2279,60 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Free text, carried through to the output board unchanged.</t>
+          <t>Sheet/column header on the output board. Blank = auto-derived.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>group_expression</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>expr</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>e.g. Stamdata.Zone='NY' .and. Stamdata.GICS, or #ALL. A bare Stamdata column is a grouping dimension; a comparison is a universe filter; .and. joins terms.</t>
+          <t>Free text, carried through to the output board unchanged.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>group_expression</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A, B, C</t>
-        </is>
-      </c>
+          <t>expr</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>A = today's dominance, B = 20d-persistent, C = 50d-persistent.</t>
+          <t>e.g. Stamdata.Zone='NY' .and. Stamdata.GICS, or #ALL. A bare Stamdata column is a grouping dimension; a comparison is a universe filter; .and. joins terms.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>persistence_window</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2644,21 +2340,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A, B, C</t>
+        </is>
+      </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Trailing daynums for B/C persistence. Default: 20 for B, 50 for C. Ignored for level A.</t>
+          <t>A = today's dominance, B = 20d-persistent, C = 50d-persistent.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>persistence_frac</t>
+          <t>persistence_window</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2666,25 +2370,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.6666666666666666</t>
-        </is>
-      </c>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Fraction of the trailing window that must have dominated (B/C only).</t>
+          <t>Trailing daynums for B/C persistence. Default: 20 for B, 50 for C. Ignored for level A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dominance_attribute</t>
+          <t>persistence_frac</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2692,25 +2392,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>0.6666666666666666</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Longi factor short name (longi_&lt;name&gt;.csv) deciding group elevation.</t>
+          <t>Fraction of the trailing window that must have dominated (B/C only).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dominance_direction</t>
+          <t>dominance_attribute</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2718,25 +2418,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>small_wins or big_wins for dominance_attribute.</t>
+          <t>Longi factor short name (longi_&lt;name&gt;.csv) deciding group elevation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dominance_decile</t>
+          <t>dominance_direction</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2744,25 +2444,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Fraction of that day's own cross-sectional distribution a ticker must be within to qualify (0.10 = best decile).</t>
+          <t>small_wins or big_wins for dominance_attribute.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dom_count_min</t>
+          <t>dominance_decile</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2770,29 +2470,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Qualifying tickers a group needs to dominate, for a group at/above 2x this many members. Below that size the requirement is HALVED relative to the group's own size (group_size/2, not rounded), not raised -- a small group needs proportionally FEWER qualifiers, not more. See step1_dominance.dom_count_threshold.</t>
+          <t>Fraction of that day's own cross-sectional distribution a ticker must be within to qualify (0.10 = best decile).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tickers_per_group</t>
+          <t>dom_count_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2807,14 +2507,14 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Top candidates drawn from EACH dominating group into the pooled test-set (per level: A=3, B=4, C=5 is SM's proposal).</t>
+          <t>Qualifying tickers a group needs to dominate, for a group at/above 2x this many members. Below that size the requirement is HALVED relative to the group's own size (group_size/2, not rounded), not raised -- a small group needs proportionally FEWER qualifiers, not more. See step1_dominance.dom_count_threshold.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>post_filter</t>
+          <t>tickers_per_group</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2822,21 +2522,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>expr</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>e.g. Longi.per1d&gt;0. Applied after Step-1 pooling; blank = none.</t>
+          <t>Top candidates drawn from EACH dominating group into the pooled test-set (per level: A=3, B=4, C=5 is SM's proposal).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>priority_attribute</t>
+          <t>post_filter</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2844,25 +2548,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
+          <t>expr</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Longi factor short name ranking candidates within/across groups.</t>
+          <t>e.g. Longi.per1d&gt;0. Applied after Step-1 pooling; blank = none.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>priority_direction</t>
+          <t>priority_attribute</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2870,25 +2570,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>small_wins or big_wins for priority_attribute.</t>
+          <t>Longi factor short name ranking candidates within/across groups.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>from_rank</t>
+          <t>priority_direction</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2896,25 +2596,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>from_rank</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Window of the ranked pool to draw the focusset from: 1=best n, -1=worst n, 'mid' or a float in (0,1)=pool-relative window, an integer k&gt;=2=fixed offset. See param_spec.parse_from_rank.</t>
+          <t>small_wins or big_wins for priority_attribute.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>focusset_size</t>
+          <t>from_rank</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2922,25 +2622,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>from_rank</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Tickers in the final pick (gross-list size 10-20 typical in production).</t>
+          <t>Window of the ranked pool to draw the focusset from: 1=best n, -1=worst n, 'mid' or a float in (0,1)=pool-relative window, an integer k&gt;=2=fixed offset. See param_spec.parse_from_rank.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stop_loss</t>
+          <t>focusset_size</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2948,55 +2648,51 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Step 3a exit level, e.g. -10. A ticker whose longi_future_minaggr&lt;period&gt;d (worst drawdown from entry) breaches this has its lot gain capped here for the rest of the hold. 0/blank = off (today's behaviour). Requires period in {20, 50} -- the only horizons minaggr covers.</t>
+          <t>Tickers in the final pick (gross-list size 10-20 typical in production).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>stop_loss</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1, 5, 10, 20, 50, 100, 200</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Forward horizon in trading days; must be a member of the seven-pack (1/5/10/20/50/100/200).</t>
+          <t>Step 3a exit level, e.g. -10. A ticker whose longi_future_minaggr&lt;period&gt;d (worst drawdown from entry) breaches this has its lot gain capped here for the rest of the hold. 0/blank = off (today's behaviour). Requires period in {20, 50} -- the only horizons minaggr covers.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>no_go_gspc_rsi</t>
+          <t>period</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3009,20 +2705,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1, 5, 10, 20, 50, 100, 200</t>
+        </is>
+      </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Suppress picks / chain hops when GSPC RSI (at daynum) &lt; this. 0 = off.</t>
+          <t>Forward horizon in trading days; must be a member of the seven-pack (1/5/10/20/50/100/200).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>informational_attributes</t>
+          <t>no_go_gspc_rsi</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3030,38 +2730,64 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>list_str</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Comma-separated Longi factor names shown for insight only; never affects selection.</t>
+          <t>Suppress picks / chain hops when GSPC RSI (at daynum) &lt; this. 0 = off.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wf_group</t>
+          <t>informational_attributes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>list_str</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Comma-separated Longi factor names shown for insight only; never affects selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>wf_group</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Candidate pool (by label, comma-separated) for selection-skill scoring. Blank = every other active row.</t>
         </is>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E527D7-1723-48BE-B866-C30F291F2620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DB0250-7B6E-4631-8ED7-584DA59D520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="1560" windowWidth="33780" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="17355" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="135">
   <si>
     <t>D</t>
   </si>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>Candidate pool (by label, comma-separated) for selection-skill scoring. Blank = every other active row.</t>
+  </si>
+  <si>
+    <t>GICS-beta3m(beta3m 1)_5</t>
   </si>
 </sst>
 </file>
@@ -819,12 +822,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="25" width="18" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -905,14 +909,11 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -970,11 +971,14 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -983,7 +987,7 @@
         <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
@@ -1021,13 +1025,16 @@
       <c r="V3" t="s">
         <v>32</v>
       </c>
+      <c r="X3" t="s">
+        <v>25</v>
+      </c>
       <c r="Y3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>34</v>
@@ -1039,10 +1046,10 @@
         <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K4">
         <v>0.1</v>
@@ -1083,7 +1090,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -1095,10 +1102,10 @@
         <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K5">
         <v>0.1</v>
@@ -1139,16 +1146,19 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
@@ -1186,10 +1196,13 @@
       <c r="V6" t="s">
         <v>32</v>
       </c>
+      <c r="Y6" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -1198,10 +1211,10 @@
         <v>29</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K7">
         <v>0.1</v>
@@ -1236,13 +1249,10 @@
       <c r="V7" t="s">
         <v>32</v>
       </c>
-      <c r="Y7" t="s">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
@@ -1251,10 +1261,10 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K8">
         <v>0.1</v>
@@ -1289,10 +1299,13 @@
       <c r="V8" t="s">
         <v>32</v>
       </c>
+      <c r="Y8" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>42</v>
@@ -1301,7 +1314,7 @@
         <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J9" t="s">
         <v>31</v>
@@ -1342,7 +1355,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -1351,7 +1364,7 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s">
         <v>31</v>
@@ -1392,7 +1405,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -1401,7 +1414,7 @@
         <v>29</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
         <v>31</v>
@@ -1442,7 +1455,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -1451,10 +1464,10 @@
         <v>29</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K12">
         <v>0.1</v>
@@ -1492,7 +1505,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
         <v>42</v>
@@ -1501,10 +1514,10 @@
         <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K13">
         <v>0.1</v>
@@ -1542,7 +1555,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -1551,7 +1564,7 @@
         <v>29</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
         <v>31</v>
@@ -1592,7 +1605,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
         <v>42</v>
@@ -1601,10 +1614,10 @@
         <v>29</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K15">
         <v>0.1</v>
@@ -1642,7 +1655,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>42</v>
@@ -1651,10 +1664,10 @@
         <v>29</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J16" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K16">
         <v>0.1</v>
@@ -1692,16 +1705,16 @@
     </row>
     <row r="17" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
       </c>
       <c r="I17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J17" t="s">
         <v>31</v>
@@ -1742,7 +1755,7 @@
     </row>
     <row r="18" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -1751,10 +1764,10 @@
         <v>29</v>
       </c>
       <c r="I18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K18">
         <v>0.1</v>
@@ -1789,25 +1802,22 @@
       <c r="V18" t="s">
         <v>32</v>
       </c>
-      <c r="Y18" t="s">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K19">
         <v>0.1</v>
@@ -1842,10 +1852,13 @@
       <c r="V19" t="s">
         <v>32</v>
       </c>
+      <c r="Y19" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -1854,7 +1867,7 @@
         <v>29</v>
       </c>
       <c r="I20" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J20" t="s">
         <v>31</v>
@@ -1895,7 +1908,7 @@
     </row>
     <row r="21" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
         <v>63</v>
@@ -1904,10 +1917,10 @@
         <v>29</v>
       </c>
       <c r="I21" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="J21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K21">
         <v>0.1</v>
@@ -1940,6 +1953,56 @@
         <v>0</v>
       </c>
       <c r="V21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22">
+        <v>0.1</v>
+      </c>
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>3</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>20</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22" t="s">
         <v>32</v>
       </c>
     </row>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DB0250-7B6E-4631-8ED7-584DA59D520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18514FD-495C-4398-BCEB-1575EAA95CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="17355" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29190" yWindow="390" windowWidth="20520" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
     <sheet name="Legend" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="133">
   <si>
     <t>D</t>
   </si>
@@ -93,18 +93,9 @@
     <t>wf_group</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>purpose</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
-    <t>GICS-beta3m(beta3m 1)</t>
-  </si>
-  <si>
     <t>Bedst</t>
   </si>
   <si>
@@ -123,27 +114,18 @@
     <t>rank, rsi, vola20d</t>
   </si>
   <si>
-    <t>GICS-PdivMA20(beta3m 1)</t>
-  </si>
-  <si>
     <t>God</t>
   </si>
   <si>
     <t>PdivMA20</t>
   </si>
   <si>
-    <t>GICS-rank(beta3m 1)</t>
-  </si>
-  <si>
     <t>rank</t>
   </si>
   <si>
     <t>small_wins</t>
   </si>
   <si>
-    <t>GICS-sh3m(beta3m 1)</t>
-  </si>
-  <si>
     <t>sh3m</t>
   </si>
   <si>
@@ -426,7 +408,19 @@
     <t>Candidate pool (by label, comma-separated) for selection-skill scoring. Blank = every other active row.</t>
   </si>
   <si>
-    <t>GICS-beta3m(beta3m 1)_5</t>
+    <t>beta6m</t>
+  </si>
+  <si>
+    <t>3m-3m stadig bedst</t>
+  </si>
+  <si>
+    <t>beta1m</t>
+  </si>
+  <si>
+    <t>beta2m</t>
+  </si>
+  <si>
+    <t>Dur ikke</t>
   </si>
 </sst>
 </file>
@@ -447,7 +441,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,11 +480,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
@@ -507,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -516,7 +505,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -822,16 +810,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="25" width="18" customWidth="1"/>
+    <col min="4" max="23" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -901,34 +889,29 @@
       <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C6" si="0">"GICS-"&amp;I2&amp;"("&amp;O2&amp;" "&amp;Q2&amp;" "&amp;R2&amp;")"</f>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K2">
         <v>0.1</v>
@@ -940,10 +923,10 @@
         <v>4</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -961,36 +944,31 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K3">
         <v>0.1</v>
@@ -1002,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1023,33 +1001,28 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>GICS-PdivMA20(beta3m 1 3)</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="Y3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K4">
         <v>0.1</v>
@@ -1061,10 +1034,10 @@
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1082,30 +1055,28 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>GICS-rank(beta3m 1 3)</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="Y4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K5">
         <v>0.1</v>
@@ -1117,10 +1088,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1138,30 +1109,28 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>GICS-sh3m(beta3m 1 3)</v>
       </c>
       <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K6">
         <v>0.1</v>
@@ -1173,10 +1142,10 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -1194,27 +1163,24 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K7">
         <v>0.1</v>
@@ -1226,10 +1192,10 @@
         <v>4</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -1247,24 +1213,24 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>0.1</v>
@@ -1276,10 +1242,10 @@
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1297,27 +1263,24 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K9">
         <v>0.1</v>
@@ -1329,10 +1292,10 @@
         <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -1350,24 +1313,24 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K10">
         <v>0.1</v>
@@ -1379,10 +1342,10 @@
         <v>4</v>
       </c>
       <c r="O10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -1400,24 +1363,24 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K11">
         <v>0.1</v>
@@ -1429,10 +1392,10 @@
         <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1450,24 +1413,24 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K12">
         <v>0.1</v>
@@ -1479,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1500,24 +1463,24 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" t="s">
-        <v>37</v>
-      </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K13">
         <v>0.1</v>
@@ -1529,10 +1492,10 @@
         <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -1550,24 +1513,24 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K14">
         <v>0.1</v>
@@ -1579,10 +1542,10 @@
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q14">
         <v>1</v>
@@ -1600,24 +1563,24 @@
         <v>0</v>
       </c>
       <c r="V14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K15">
         <v>0.1</v>
@@ -1629,10 +1592,10 @@
         <v>4</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -1650,24 +1613,24 @@
         <v>0</v>
       </c>
       <c r="V15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K16">
         <v>0.1</v>
@@ -1679,10 +1642,10 @@
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -1700,24 +1663,24 @@
         <v>0</v>
       </c>
       <c r="V16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K17">
         <v>0.1</v>
@@ -1729,10 +1692,10 @@
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q17">
         <v>1</v>
@@ -1750,24 +1713,24 @@
         <v>0</v>
       </c>
       <c r="V17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K18">
         <v>0.1</v>
@@ -1779,10 +1742,10 @@
         <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q18">
         <v>1</v>
@@ -1800,24 +1763,24 @@
         <v>0</v>
       </c>
       <c r="V18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K19">
         <v>0.1</v>
@@ -1829,10 +1792,10 @@
         <v>4</v>
       </c>
       <c r="O19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q19">
         <v>1</v>
@@ -1850,27 +1813,24 @@
         <v>0</v>
       </c>
       <c r="V19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K20">
         <v>0.1</v>
@@ -1882,10 +1842,10 @@
         <v>4</v>
       </c>
       <c r="O20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>1</v>
@@ -1903,24 +1863,24 @@
         <v>0</v>
       </c>
       <c r="V20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K21">
         <v>0.1</v>
@@ -1932,10 +1892,10 @@
         <v>4</v>
       </c>
       <c r="O21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -1953,24 +1913,24 @@
         <v>0</v>
       </c>
       <c r="V21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K22">
         <v>0.1</v>
@@ -1982,10 +1942,10 @@
         <v>4</v>
       </c>
       <c r="O22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q22">
         <v>1</v>
@@ -2003,7 +1963,277 @@
         <v>0</v>
       </c>
       <c r="V22" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C23" t="str">
+        <f>"GICS-"&amp;I23&amp;"("&amp;O23&amp;" "&amp;Q23&amp;" "&amp;R23&amp;")"</f>
+        <v>GICS-beta6m(beta6m 1 3)</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23">
+        <v>0.1</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="O23" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>20</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C24" t="str">
+        <f>"GICS-"&amp;I24&amp;"("&amp;O24&amp;" "&amp;Q24&amp;" "&amp;R24&amp;")"</f>
+        <v>GICS-beta3m(beta6m 1 3)</v>
+      </c>
+      <c r="D24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24">
+        <v>0.1</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="O24" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>20</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C25" t="str">
+        <f>"GICS-"&amp;I25&amp;"("&amp;O25&amp;" "&amp;Q25&amp;" "&amp;R25&amp;")"</f>
+        <v>GICS-beta6m(beta3m 1 3)</v>
+      </c>
+      <c r="D25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25">
+        <v>0.1</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="O25" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>3</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>20</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C26" t="str">
+        <f t="shared" ref="C26:C27" si="1">"GICS-"&amp;I26&amp;"("&amp;O26&amp;" "&amp;Q26&amp;" "&amp;R26&amp;")"</f>
+        <v>GICS-beta1m(beta1m 1 3)</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" t="s">
+        <v>130</v>
+      </c>
+      <c r="J26" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26">
+        <v>0.1</v>
+      </c>
+      <c r="L26">
+        <v>10</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="O26" t="s">
+        <v>130</v>
+      </c>
+      <c r="P26" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>3</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>20</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C27" t="str">
+        <f t="shared" si="1"/>
+        <v>GICS-beta2m(beta2m 1 3)</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" t="s">
+        <v>131</v>
+      </c>
+      <c r="J27" t="s">
+        <v>28</v>
+      </c>
+      <c r="K27">
+        <v>0.1</v>
+      </c>
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="O27" t="s">
+        <v>131</v>
+      </c>
+      <c r="P27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>20</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2022,91 +2252,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>68</v>
+      <c r="A1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>70</v>
+      <c r="C2" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>315</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>72</v>
+      <c r="C3" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>63</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>74</v>
+      <c r="C4" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>76</v>
+      <c r="C5" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>78</v>
+      <c r="C6" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>83</v>
+      <c r="C8" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2128,23 +2358,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>68</v>
+      <c r="A1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2152,16 +2382,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>92</v>
+        <v>85</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2169,16 +2399,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2186,13 +2416,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2200,13 +2430,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2217,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,16 +2461,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,10 +2481,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2265,13 +2495,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2282,13 +2512,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>107</v>
+        <v>32</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2299,13 +2529,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2316,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2333,13 +2563,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2350,13 +2580,13 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2367,10 +2597,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>116</v>
+        <v>91</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2381,13 +2611,13 @@
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>117</v>
+        <v>32</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2398,13 +2628,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>118</v>
+        <v>103</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2418,10 +2648,10 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,13 +2662,13 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2449,13 +2679,13 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,16 +2696,16 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,13 +2716,13 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,13 +2733,13 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2520,10 +2750,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>133</v>
+        <v>88</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18514FD-495C-4398-BCEB-1575EAA95CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD194352-9FE0-4915-9D63-3EA559AA8A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29190" yWindow="390" windowWidth="20520" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20535" yWindow="1875" windowWidth="33870" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="138">
   <si>
     <t>D</t>
   </si>
@@ -421,6 +421,21 @@
   </si>
   <si>
     <t>Dur ikke</t>
+  </si>
+  <si>
+    <t>Stamdata.GICS .and. Stamdata.Zone="LON"</t>
+  </si>
+  <si>
+    <t>Longi.rank&lt;1000</t>
+  </si>
+  <si>
+    <t>Bedst LON</t>
+  </si>
+  <si>
+    <t>Næstbedst LON</t>
+  </si>
+  <si>
+    <t>næstbedst LON</t>
   </si>
 </sst>
 </file>
@@ -441,7 +456,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +498,12 @@
         <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -496,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -508,6 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1666,7 +1688,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>52</v>
       </c>
@@ -1716,7 +1738,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>54</v>
       </c>
@@ -1766,7 +1788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>55</v>
       </c>
@@ -1816,7 +1838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>56</v>
       </c>
@@ -1866,7 +1888,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>58</v>
       </c>
@@ -1916,7 +1938,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -1966,7 +1988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>"GICS-"&amp;I23&amp;"("&amp;O23&amp;" "&amp;Q23&amp;" "&amp;R23&amp;")"</f>
         <v>GICS-beta6m(beta6m 1 3)</v>
@@ -2020,7 +2042,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C24" t="str">
         <f>"GICS-"&amp;I24&amp;"("&amp;O24&amp;" "&amp;Q24&amp;" "&amp;R24&amp;")"</f>
         <v>GICS-beta3m(beta6m 1 3)</v>
@@ -2074,7 +2096,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C25" t="str">
         <f>"GICS-"&amp;I25&amp;"("&amp;O25&amp;" "&amp;Q25&amp;" "&amp;R25&amp;")"</f>
         <v>GICS-beta6m(beta3m 1 3)</v>
@@ -2128,7 +2150,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C26" t="str">
         <f t="shared" ref="C26:C27" si="1">"GICS-"&amp;I26&amp;"("&amp;O26&amp;" "&amp;Q26&amp;" "&amp;R26&amp;")"</f>
         <v>GICS-beta1m(beta1m 1 3)</v>
@@ -2182,7 +2204,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C27" t="str">
         <f t="shared" si="1"/>
         <v>GICS-beta2m(beta2m 1 3)</v>
@@ -2233,6 +2255,888 @@
         <v>0</v>
       </c>
       <c r="V27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C28" t="str">
+        <f>"GICS-LON " &amp;I28&amp;"("&amp;O28&amp;" "&amp;Q28&amp;" "&amp;R28&amp;")"</f>
+        <v>GICS-LON beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="E28" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28">
+        <v>0.1</v>
+      </c>
+      <c r="L28">
+        <v>5</v>
+      </c>
+      <c r="M28">
+        <v>4</v>
+      </c>
+      <c r="N28" t="s">
+        <v>134</v>
+      </c>
+      <c r="O28" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>3</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>20</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C29" t="str">
+        <f t="shared" ref="C29:C33" si="2">"GICS-LON " &amp;I29&amp;"("&amp;O29&amp;" "&amp;Q29&amp;" "&amp;R29&amp;")"</f>
+        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29">
+        <v>0.1</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29" t="s">
+        <v>134</v>
+      </c>
+      <c r="O29" t="s">
+        <v>27</v>
+      </c>
+      <c r="P29" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <v>3</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>20</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="9">
+        <v>5</v>
+      </c>
+      <c r="M30" s="9">
+        <v>4</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>1</v>
+      </c>
+      <c r="R30" s="9">
+        <v>3</v>
+      </c>
+      <c r="S30" s="9">
+        <v>0</v>
+      </c>
+      <c r="T30" s="9">
+        <v>20</v>
+      </c>
+      <c r="U30" s="9">
+        <v>0</v>
+      </c>
+      <c r="V30" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C31" t="str">
+        <f t="shared" si="2"/>
+        <v>GICS-LON sh3m(beta3m 1 3)</v>
+      </c>
+      <c r="E31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" t="s">
+        <v>28</v>
+      </c>
+      <c r="K31">
+        <v>0.1</v>
+      </c>
+      <c r="L31">
+        <v>5</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>3</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>20</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C32" t="str">
+        <f t="shared" si="2"/>
+        <v>GICS-LON rsi(beta3m 1 3)</v>
+      </c>
+      <c r="E32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32">
+        <v>0.1</v>
+      </c>
+      <c r="L32">
+        <v>5</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>3</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>20</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C33" t="str">
+        <f t="shared" si="2"/>
+        <v>GICS-LON spr100d(beta3m 1 3)</v>
+      </c>
+      <c r="E33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33">
+        <v>0.1</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+      <c r="M33">
+        <v>4</v>
+      </c>
+      <c r="N33" t="s">
+        <v>134</v>
+      </c>
+      <c r="O33" t="s">
+        <v>27</v>
+      </c>
+      <c r="P33" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>3</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>20</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C34" t="str">
+        <f t="shared" ref="C34:C36" si="3">"GICS-LON " &amp;I34&amp;"("&amp;O34&amp;" "&amp;Q34&amp;" "&amp;R34&amp;")"</f>
+        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
+      </c>
+      <c r="E34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" t="s">
+        <v>28</v>
+      </c>
+      <c r="K34">
+        <v>0.1</v>
+      </c>
+      <c r="L34">
+        <v>5</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="O34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>3</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>20</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K35" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L35" s="9">
+        <v>5</v>
+      </c>
+      <c r="M35" s="9">
+        <v>4</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>1</v>
+      </c>
+      <c r="R35" s="9">
+        <v>3</v>
+      </c>
+      <c r="S35" s="9">
+        <v>0</v>
+      </c>
+      <c r="T35" s="9">
+        <v>20</v>
+      </c>
+      <c r="U35" s="9">
+        <v>0</v>
+      </c>
+      <c r="V35" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C36" t="str">
+        <f t="shared" si="3"/>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36">
+        <v>0.1</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+      <c r="M36">
+        <v>4</v>
+      </c>
+      <c r="N36" t="s">
+        <v>134</v>
+      </c>
+      <c r="O36" t="s">
+        <v>31</v>
+      </c>
+      <c r="P36" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>3</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>20</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C37" t="str">
+        <f t="shared" ref="C37:C40" si="4">"GICS-LON " &amp;I37&amp;"("&amp;O37&amp;" "&amp;Q37&amp;" "&amp;R37&amp;")"</f>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D37" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37">
+        <v>0.1</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="O37" t="s">
+        <v>31</v>
+      </c>
+      <c r="P37" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>3</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>20</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C38" t="str">
+        <f t="shared" si="4"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38">
+        <v>0.2</v>
+      </c>
+      <c r="L38">
+        <v>5</v>
+      </c>
+      <c r="M38">
+        <v>4</v>
+      </c>
+      <c r="N38" t="s">
+        <v>134</v>
+      </c>
+      <c r="O38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>3</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>20</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C39" t="str">
+        <f t="shared" si="4"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D39" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39">
+        <v>0.2</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>3</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>20</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C40" t="str">
+        <f t="shared" si="4"/>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40">
+        <v>0.1</v>
+      </c>
+      <c r="L40">
+        <v>3</v>
+      </c>
+      <c r="M40">
+        <v>4</v>
+      </c>
+      <c r="N40" t="s">
+        <v>134</v>
+      </c>
+      <c r="O40" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <v>3</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>20</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C41" t="str">
+        <f t="shared" ref="C41:C42" si="5">"GICS-LON " &amp;I41&amp;"("&amp;O41&amp;" "&amp;Q41&amp;" "&amp;R41&amp;")"</f>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D41" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41">
+        <v>0.1</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41">
+        <v>4</v>
+      </c>
+      <c r="O41" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>3</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>20</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C42" t="str">
+        <f t="shared" si="5"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D42" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>33</v>
+      </c>
+      <c r="K42">
+        <v>0.1</v>
+      </c>
+      <c r="L42">
+        <v>3</v>
+      </c>
+      <c r="M42">
+        <v>4</v>
+      </c>
+      <c r="N42" t="s">
+        <v>134</v>
+      </c>
+      <c r="O42" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <v>3</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>20</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C43" t="str">
+        <f t="shared" ref="C43" si="6">"GICS-LON " &amp;I43&amp;"("&amp;O43&amp;" "&amp;Q43&amp;" "&amp;R43&amp;")"</f>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43">
+        <v>0.1</v>
+      </c>
+      <c r="L43">
+        <v>3</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="O43" t="s">
+        <v>27</v>
+      </c>
+      <c r="P43" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>3</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>20</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43" t="s">
         <v>29</v>
       </c>
     </row>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD194352-9FE0-4915-9D63-3EA559AA8A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECFFA95-FF41-422D-9768-8CAB2092B46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20535" yWindow="1875" windowWidth="33870" windowHeight="14265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21675" yWindow="1530" windowWidth="34875" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="148">
   <si>
     <t>D</t>
   </si>
@@ -429,20 +429,50 @@
     <t>Longi.rank&lt;1000</t>
   </si>
   <si>
-    <t>Bedst LON</t>
-  </si>
-  <si>
     <t>Næstbedst LON</t>
   </si>
   <si>
     <t>næstbedst LON</t>
+  </si>
+  <si>
+    <t>Godt gain, dårlig extension</t>
+  </si>
+  <si>
+    <t>rank, per1d, regr20d, regr50d</t>
+  </si>
+  <si>
+    <t>Longi.per1d&gt;0</t>
+  </si>
+  <si>
+    <t>Longi.regr20d&gt;0</t>
+  </si>
+  <si>
+    <t>Longi.regr50d&gt;0</t>
+  </si>
+  <si>
+    <t>Longi.median_10d&lt;1100</t>
+  </si>
+  <si>
+    <t>Longi.median_10d&lt;1000</t>
+  </si>
+  <si>
+    <t>extension dør</t>
+  </si>
+  <si>
+    <t>rank, regr20d, regr50d, regr100d, regr200d</t>
+  </si>
+  <si>
+    <t>Longi.beta3m&gt;2.5</t>
+  </si>
+  <si>
+    <t>Longi.beta3m&gt;3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,8 +485,15 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,8 +541,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -513,11 +555,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -529,10 +605,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -832,13 +911,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="23" width="18" customWidth="1"/>
+    <col min="4" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="27.85546875" customWidth="1"/>
+    <col min="15" max="23" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -917,8 +998,8 @@
         <v>23</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C6" si="0">"GICS-"&amp;I2&amp;"("&amp;O2&amp;" "&amp;Q2&amp;" "&amp;R2&amp;")"</f>
-        <v>GICS-beta3m(beta3m 1 3)</v>
+        <f>"GICS-"&amp;I2&amp;"("&amp;O2&amp;"), test  "&amp;R2&amp;")"</f>
+        <v>GICS-beta3m(beta3m), test  3)</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -944,6 +1025,9 @@
       <c r="M2">
         <v>4</v>
       </c>
+      <c r="N2" t="s">
+        <v>146</v>
+      </c>
       <c r="O2" t="s">
         <v>27</v>
       </c>
@@ -966,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -974,7 +1058,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C3:C7" si="0">"GICS-"&amp;I3&amp;"("&amp;O3&amp;" "&amp;Q3&amp;" "&amp;R3&amp;")"</f>
         <v>GICS-beta3m(beta3m 1 3)</v>
       </c>
       <c r="D3" t="s">
@@ -1001,6 +1085,9 @@
       <c r="M3">
         <v>4</v>
       </c>
+      <c r="N3" t="s">
+        <v>146</v>
+      </c>
       <c r="O3" t="s">
         <v>27</v>
       </c>
@@ -1023,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>GICS-PdivMA20(beta3m 1 3)</v>
+        <f>"GICS-"&amp;I4&amp;"("&amp;O4&amp;"), test  "&amp;R4&amp;")"</f>
+        <v>GICS-rank(beta3m), test  3)</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -1041,10 +1128,10 @@
         <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K4">
         <v>0.1</v>
@@ -1055,6 +1142,9 @@
       <c r="M4">
         <v>4</v>
       </c>
+      <c r="N4" t="s">
+        <v>146</v>
+      </c>
       <c r="O4" t="s">
         <v>27</v>
       </c>
@@ -1077,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -1109,6 +1199,9 @@
       <c r="M5">
         <v>4</v>
       </c>
+      <c r="N5" t="s">
+        <v>147</v>
+      </c>
       <c r="O5" t="s">
         <v>27</v>
       </c>
@@ -1130,76 +1223,80 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
-        <v>29</v>
+      <c r="V5" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C6" t="str">
+        <f>"GICS-"&amp;I6&amp;"("&amp;O6&amp;"), test  "&amp;R6&amp;")"</f>
+        <v>GICS-PdivMA20(beta3m), test  3)</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>0.1</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C7" t="str">
         <f t="shared" si="0"/>
         <v>GICS-sh3m(beta3m 1 3)</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
         <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6">
-        <v>0.1</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>20</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -1240,7 +1337,7 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
@@ -1249,10 +1346,10 @@
         <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K8">
         <v>0.1</v>
@@ -1290,7 +1387,7 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1299,10 +1396,10 @@
         <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K9">
         <v>0.1</v>
@@ -1340,7 +1437,7 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
@@ -1349,7 +1446,7 @@
         <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
         <v>28</v>
@@ -1390,7 +1487,7 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -1399,7 +1496,7 @@
         <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
@@ -1440,7 +1537,7 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -1449,7 +1546,7 @@
         <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
         <v>28</v>
@@ -1490,7 +1587,7 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -1499,10 +1596,10 @@
         <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K13">
         <v>0.1</v>
@@ -1540,7 +1637,7 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -1549,10 +1646,10 @@
         <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K14">
         <v>0.1</v>
@@ -1590,7 +1687,7 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -1599,7 +1696,7 @@
         <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J15" t="s">
         <v>28</v>
@@ -1640,7 +1737,7 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
@@ -1649,10 +1746,10 @@
         <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K16">
         <v>0.1</v>
@@ -1688,9 +1785,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -1699,10 +1796,10 @@
         <v>26</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K17">
         <v>0.1</v>
@@ -1738,18 +1835,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
         <v>28</v>
@@ -1788,9 +1885,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -1799,10 +1896,10 @@
         <v>26</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K19">
         <v>0.1</v>
@@ -1838,21 +1935,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K20">
         <v>0.1</v>
@@ -1888,9 +1985,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
         <v>57</v>
@@ -1899,7 +1996,7 @@
         <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J21" t="s">
         <v>28</v>
@@ -1938,9 +2035,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
         <v>57</v>
@@ -1949,10 +2046,10 @@
         <v>26</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K22">
         <v>0.1</v>
@@ -1988,25 +2085,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C23" t="str">
-        <f>"GICS-"&amp;I23&amp;"("&amp;O23&amp;" "&amp;Q23&amp;" "&amp;R23&amp;")"</f>
-        <v>GICS-beta6m(beta6m 1 3)</v>
-      </c>
-      <c r="D23" t="s">
-        <v>129</v>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="I23" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="J23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K23">
         <v>0.1</v>
@@ -2018,7 +2111,7 @@
         <v>4</v>
       </c>
       <c r="O23" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="P23" t="s">
         <v>28</v>
@@ -2042,10 +2135,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C24" t="str">
         <f>"GICS-"&amp;I24&amp;"("&amp;O24&amp;" "&amp;Q24&amp;" "&amp;R24&amp;")"</f>
-        <v>GICS-beta3m(beta6m 1 3)</v>
+        <v>GICS-beta6m(beta6m 1 3)</v>
       </c>
       <c r="D24" t="s">
         <v>129</v>
@@ -2057,7 +2150,7 @@
         <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="J24" t="s">
         <v>28</v>
@@ -2096,10 +2189,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C25" t="str">
         <f>"GICS-"&amp;I25&amp;"("&amp;O25&amp;" "&amp;Q25&amp;" "&amp;R25&amp;")"</f>
-        <v>GICS-beta6m(beta3m 1 3)</v>
+        <v>GICS-beta3m(beta6m 1 3)</v>
       </c>
       <c r="D25" t="s">
         <v>129</v>
@@ -2111,7 +2204,7 @@
         <v>26</v>
       </c>
       <c r="I25" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="J25" t="s">
         <v>28</v>
@@ -2126,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="O25" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="P25" t="s">
         <v>28</v>
@@ -2150,13 +2243,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C26" t="str">
-        <f t="shared" ref="C26:C27" si="1">"GICS-"&amp;I26&amp;"("&amp;O26&amp;" "&amp;Q26&amp;" "&amp;R26&amp;")"</f>
-        <v>GICS-beta1m(beta1m 1 3)</v>
+        <f>"GICS-"&amp;I26&amp;"("&amp;O26&amp;" "&amp;Q26&amp;" "&amp;R26&amp;")"</f>
+        <v>GICS-beta6m(beta3m 1 3)</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -2165,7 +2258,7 @@
         <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J26" t="s">
         <v>28</v>
@@ -2180,7 +2273,7 @@
         <v>4</v>
       </c>
       <c r="O26" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="P26" t="s">
         <v>28</v>
@@ -2204,91 +2297,91 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C27" t="str">
+        <f t="shared" ref="C27:C28" si="1">"GICS-"&amp;I27&amp;"("&amp;O27&amp;" "&amp;Q27&amp;" "&amp;R27&amp;")"</f>
+        <v>GICS-beta1m(beta1m 1 3)</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" t="s">
+        <v>130</v>
+      </c>
+      <c r="J27" t="s">
+        <v>28</v>
+      </c>
+      <c r="K27">
+        <v>0.1</v>
+      </c>
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="O27" t="s">
+        <v>130</v>
+      </c>
+      <c r="P27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>20</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C28" t="str">
         <f t="shared" si="1"/>
         <v>GICS-beta2m(beta2m 1 3)</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>132</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>25</v>
       </c>
-      <c r="F27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
         <v>131</v>
       </c>
-      <c r="J27" t="s">
-        <v>28</v>
-      </c>
-      <c r="K27">
-        <v>0.1</v>
-      </c>
-      <c r="L27">
+      <c r="J28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28">
+        <v>0.1</v>
+      </c>
+      <c r="L28">
         <v>10</v>
       </c>
-      <c r="M27">
-        <v>4</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="M28">
+        <v>4</v>
+      </c>
+      <c r="O28" t="s">
         <v>131</v>
-      </c>
-      <c r="P27" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <v>3</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>20</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C28" t="str">
-        <f>"GICS-LON " &amp;I28&amp;"("&amp;O28&amp;" "&amp;Q28&amp;" "&amp;R28&amp;")"</f>
-        <v>GICS-LON beta3m(beta3m 1 3)</v>
-      </c>
-      <c r="E28" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I28" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" t="s">
-        <v>28</v>
-      </c>
-      <c r="K28">
-        <v>0.1</v>
-      </c>
-      <c r="L28">
-        <v>5</v>
-      </c>
-      <c r="M28">
-        <v>4</v>
-      </c>
-      <c r="N28" t="s">
-        <v>134</v>
-      </c>
-      <c r="O28" t="s">
-        <v>27</v>
       </c>
       <c r="P28" t="s">
         <v>28</v>
@@ -2312,13 +2405,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C29" t="str">
-        <f t="shared" ref="C29:C33" si="2">"GICS-LON " &amp;I29&amp;"("&amp;O29&amp;" "&amp;Q29&amp;" "&amp;R29&amp;")"</f>
-        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
+        <f>"GICS-LON " &amp;I29&amp;"("&amp;O29&amp;" "&amp;Q29&amp;" "&amp;R29&amp;")"</f>
+        <v>GICS-LON beta3m(beta3m 1 3)</v>
       </c>
       <c r="E29" t="s">
         <v>133</v>
@@ -2327,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J29" t="s">
         <v>28</v>
@@ -2369,125 +2459,125 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="9" t="str">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C30" t="str">
+        <f t="shared" ref="C30:C34" si="2">"GICS-LON " &amp;I30&amp;"("&amp;O30&amp;" "&amp;Q30&amp;" "&amp;R30&amp;")"</f>
+        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30">
+        <v>0.1</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30">
+        <v>4</v>
+      </c>
+      <c r="N30" t="s">
+        <v>134</v>
+      </c>
+      <c r="O30" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <v>3</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>20</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C31" t="str">
         <f t="shared" si="2"/>
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="9" t="s">
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I30" s="9" t="s">
+      <c r="F31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J31" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="L30" s="9">
+      <c r="K31">
+        <v>0.1</v>
+      </c>
+      <c r="L31">
         <v>5</v>
       </c>
-      <c r="M30" s="9">
-        <v>4</v>
-      </c>
-      <c r="N30" s="9" t="s">
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31" t="s">
         <v>134</v>
       </c>
-      <c r="O30" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>1</v>
-      </c>
-      <c r="R30" s="9">
-        <v>3</v>
-      </c>
-      <c r="S30" s="9">
-        <v>0</v>
-      </c>
-      <c r="T30" s="9">
-        <v>20</v>
-      </c>
-      <c r="U30" s="9">
-        <v>0</v>
-      </c>
-      <c r="V30" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C31" t="str">
+      <c r="O31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>3</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>20</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C32" t="str">
         <f t="shared" si="2"/>
         <v>GICS-LON sh3m(beta3m 1 3)</v>
       </c>
-      <c r="E31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F31" t="s">
-        <v>26</v>
-      </c>
-      <c r="I31" t="s">
-        <v>34</v>
-      </c>
-      <c r="J31" t="s">
-        <v>28</v>
-      </c>
-      <c r="K31">
-        <v>0.1</v>
-      </c>
-      <c r="L31">
-        <v>5</v>
-      </c>
-      <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31" t="s">
-        <v>134</v>
-      </c>
-      <c r="O31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31">
-        <v>3</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>20</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C32" t="str">
-        <f t="shared" si="2"/>
-        <v>GICS-LON rsi(beta3m 1 3)</v>
-      </c>
       <c r="E32" t="s">
         <v>133</v>
       </c>
@@ -2495,7 +2585,7 @@
         <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J32" t="s">
         <v>28</v>
@@ -2540,7 +2630,7 @@
     <row r="33" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C33" t="str">
         <f t="shared" si="2"/>
-        <v>GICS-LON spr100d(beta3m 1 3)</v>
+        <v>GICS-LON rsi(beta3m 1 3)</v>
       </c>
       <c r="E33" t="s">
         <v>133</v>
@@ -2549,10 +2639,10 @@
         <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K33">
         <v>0.1</v>
@@ -2593,8 +2683,8 @@
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" t="str">
-        <f t="shared" ref="C34:C36" si="3">"GICS-LON " &amp;I34&amp;"("&amp;O34&amp;" "&amp;Q34&amp;" "&amp;R34&amp;")"</f>
-        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
+        <f t="shared" si="2"/>
+        <v>GICS-LON spr100d(beta3m 1 3)</v>
       </c>
       <c r="E34" t="s">
         <v>133</v>
@@ -2603,10 +2693,10 @@
         <v>26</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K34">
         <v>0.1</v>
@@ -2617,6 +2707,9 @@
       <c r="M34">
         <v>4</v>
       </c>
+      <c r="N34" t="s">
+        <v>134</v>
+      </c>
       <c r="O34" t="s">
         <v>27</v>
       </c>
@@ -2642,67 +2735,64 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="9" t="str">
-        <f t="shared" si="3"/>
+    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C35" t="str">
+        <f t="shared" ref="C35" si="3">"GICS-LON " &amp;I35&amp;"("&amp;O35&amp;" "&amp;Q35&amp;" "&amp;R35&amp;")"</f>
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="9" t="s">
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
         <v>32</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" t="s">
         <v>33</v>
       </c>
-      <c r="K35" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="L35" s="9">
+      <c r="K35">
+        <v>0.1</v>
+      </c>
+      <c r="L35">
         <v>5</v>
       </c>
-      <c r="M35" s="9">
-        <v>4</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>1</v>
-      </c>
-      <c r="R35" s="9">
-        <v>3</v>
-      </c>
-      <c r="S35" s="9">
-        <v>0</v>
-      </c>
-      <c r="T35" s="9">
-        <v>20</v>
-      </c>
-      <c r="U35" s="9">
-        <v>0</v>
-      </c>
-      <c r="V35" s="9" t="s">
-        <v>29</v>
+      <c r="M35">
+        <v>4</v>
+      </c>
+      <c r="O35" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>3</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>20</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C36" t="str">
-        <f t="shared" si="3"/>
-        <v>GICS-LON rank(PdivMA20 1 3)</v>
+        <f t="shared" ref="C36" si="4">"GICS-LON " &amp;I36&amp;"("&amp;O36&amp;" "&amp;Q36&amp;" "&amp;R36&amp;")"</f>
+        <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
         <v>133</v>
@@ -2726,10 +2816,10 @@
         <v>4</v>
       </c>
       <c r="N36" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="O36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P36" t="s">
         <v>28</v>
@@ -2750,16 +2840,13 @@
         <v>0</v>
       </c>
       <c r="V36" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C37" t="str">
-        <f t="shared" ref="C37:C40" si="4">"GICS-LON " &amp;I37&amp;"("&amp;O37&amp;" "&amp;Q37&amp;" "&amp;R37&amp;")"</f>
-        <v>GICS-LON rank(PdivMA20 1 3)</v>
-      </c>
-      <c r="D37" t="s">
-        <v>132</v>
+        <f t="shared" ref="C37" si="5">"GICS-LON " &amp;I37&amp;"("&amp;O37&amp;" "&amp;Q37&amp;" "&amp;R37&amp;")"</f>
+        <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="E37" t="s">
         <v>133</v>
@@ -2782,8 +2869,11 @@
       <c r="M37">
         <v>4</v>
       </c>
+      <c r="N37" t="s">
+        <v>140</v>
+      </c>
       <c r="O37" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P37" t="s">
         <v>28</v>
@@ -2804,16 +2894,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C38" si="6">"GICS-LON " &amp;I38&amp;"("&amp;O38&amp;" "&amp;Q38&amp;" "&amp;R38&amp;")"</f>
         <v>GICS-LON rank(beta3m 1 3)</v>
-      </c>
-      <c r="D38" t="s">
-        <v>132</v>
       </c>
       <c r="E38" t="s">
         <v>133</v>
@@ -2828,7 +2915,7 @@
         <v>33</v>
       </c>
       <c r="K38">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -2837,7 +2924,7 @@
         <v>4</v>
       </c>
       <c r="N38" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="O38" t="s">
         <v>27</v>
@@ -2861,16 +2948,16 @@
         <v>0</v>
       </c>
       <c r="V38" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C39" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C39" si="7">"GICS-LON " &amp;I39&amp;"("&amp;O39&amp;" "&amp;Q39&amp;" "&amp;R39&amp;")"</f>
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
         <v>133</v>
@@ -2885,7 +2972,7 @@
         <v>33</v>
       </c>
       <c r="K39">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -2893,6 +2980,9 @@
       <c r="M39">
         <v>4</v>
       </c>
+      <c r="N39" t="s">
+        <v>142</v>
+      </c>
       <c r="O39" t="s">
         <v>27</v>
       </c>
@@ -2915,16 +3005,16 @@
         <v>0</v>
       </c>
       <c r="V39" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C40" t="str">
-        <f t="shared" si="4"/>
-        <v>GICS-LON rank(PdivMA20 1 3)</v>
+        <f t="shared" ref="C40" si="8">"GICS-LON " &amp;I40&amp;"("&amp;O40&amp;" "&amp;Q40&amp;" "&amp;R40&amp;")"</f>
+        <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
@@ -2942,16 +3032,16 @@
         <v>0.1</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>4</v>
       </c>
       <c r="N40" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="O40" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P40" t="s">
         <v>28</v>
@@ -2972,16 +3062,13 @@
         <v>0</v>
       </c>
       <c r="V40" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C41" t="str">
-        <f t="shared" ref="C41:C42" si="5">"GICS-LON " &amp;I41&amp;"("&amp;O41&amp;" "&amp;Q41&amp;" "&amp;R41&amp;")"</f>
-        <v>GICS-LON rank(PdivMA20 1 3)</v>
-      </c>
-      <c r="D41" t="s">
-        <v>132</v>
+        <f t="shared" ref="C41" si="9">"GICS-LON " &amp;I41&amp;"("&amp;O41&amp;" "&amp;Q41&amp;" "&amp;R41&amp;")"</f>
+        <v>GICS-LON PdivMA20(beta3m 1 3)</v>
       </c>
       <c r="E41" t="s">
         <v>133</v>
@@ -2990,22 +3077,22 @@
         <v>26</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J41" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K41">
         <v>0.1</v>
       </c>
       <c r="L41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>4</v>
       </c>
       <c r="O41" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P41" t="s">
         <v>28</v>
@@ -3029,67 +3116,64 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C42" t="str">
-        <f t="shared" si="5"/>
+    <row r="42" spans="3:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="10" t="str">
+        <f t="shared" ref="C42:C43" si="10">"GICS-LON " &amp;I42&amp;"("&amp;O42&amp;" "&amp;Q42&amp;" "&amp;R42&amp;")"</f>
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="D42" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E42" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="F42" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="K42">
-        <v>0.1</v>
-      </c>
-      <c r="L42">
-        <v>3</v>
-      </c>
-      <c r="M42">
-        <v>4</v>
-      </c>
-      <c r="N42" t="s">
-        <v>134</v>
-      </c>
-      <c r="O42" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42">
-        <v>3</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>20</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42" t="s">
-        <v>29</v>
+      <c r="K42" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="10">
+        <v>5</v>
+      </c>
+      <c r="M42" s="10">
+        <v>4</v>
+      </c>
+      <c r="O42" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>1</v>
+      </c>
+      <c r="R42" s="10">
+        <v>3</v>
+      </c>
+      <c r="S42" s="10">
+        <v>0</v>
+      </c>
+      <c r="T42" s="10">
+        <v>20</v>
+      </c>
+      <c r="U42" s="10">
+        <v>0</v>
+      </c>
+      <c r="V42" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C43" t="str">
-        <f t="shared" ref="C43" si="6">"GICS-LON " &amp;I43&amp;"("&amp;O43&amp;" "&amp;Q43&amp;" "&amp;R43&amp;")"</f>
-        <v>GICS-LON rank(beta3m 1 3)</v>
+        <f t="shared" si="10"/>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
       </c>
       <c r="D43" t="s">
         <v>132</v>
@@ -3110,13 +3194,16 @@
         <v>0.1</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>4</v>
       </c>
+      <c r="N43" t="s">
+        <v>134</v>
+      </c>
       <c r="O43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="P43" t="s">
         <v>28</v>
@@ -3138,6 +3225,609 @@
       </c>
       <c r="V43" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C44" t="str">
+        <f t="shared" ref="C44:C47" si="11">"GICS-LON " &amp;I44&amp;"("&amp;O44&amp;" "&amp;Q44&amp;" "&amp;R44&amp;")"</f>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D44" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
+        <v>33</v>
+      </c>
+      <c r="K44">
+        <v>0.1</v>
+      </c>
+      <c r="L44">
+        <v>5</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="O44" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <v>3</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>20</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C45" t="str">
+        <f t="shared" si="11"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D45" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45">
+        <v>0.2</v>
+      </c>
+      <c r="L45">
+        <v>5</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45" t="s">
+        <v>134</v>
+      </c>
+      <c r="O45" t="s">
+        <v>27</v>
+      </c>
+      <c r="P45" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>20</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C46" t="str">
+        <f t="shared" si="11"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D46" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" t="s">
+        <v>33</v>
+      </c>
+      <c r="K46">
+        <v>0.2</v>
+      </c>
+      <c r="L46">
+        <v>5</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+      <c r="O46" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46">
+        <v>3</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>20</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C47" t="str">
+        <f t="shared" si="11"/>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D47" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47">
+        <v>0.1</v>
+      </c>
+      <c r="L47">
+        <v>3</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47" t="s">
+        <v>134</v>
+      </c>
+      <c r="O47" t="s">
+        <v>31</v>
+      </c>
+      <c r="P47" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>20</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C48" t="str">
+        <f t="shared" ref="C48:C50" si="12">"GICS-LON " &amp;I48&amp;"("&amp;O48&amp;" "&amp;Q48&amp;" "&amp;R48&amp;")"</f>
+        <v>GICS-LON rank(PdivMA20 1 3)</v>
+      </c>
+      <c r="D48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F48" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48">
+        <v>0.1</v>
+      </c>
+      <c r="L48">
+        <v>3</v>
+      </c>
+      <c r="M48">
+        <v>4</v>
+      </c>
+      <c r="O48" t="s">
+        <v>31</v>
+      </c>
+      <c r="P48" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <v>3</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>20</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C49" t="str">
+        <f t="shared" si="12"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D49" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49">
+        <v>0.1</v>
+      </c>
+      <c r="L49">
+        <v>3</v>
+      </c>
+      <c r="M49">
+        <v>4</v>
+      </c>
+      <c r="N49" t="s">
+        <v>134</v>
+      </c>
+      <c r="O49" t="s">
+        <v>27</v>
+      </c>
+      <c r="P49" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
+      <c r="R49">
+        <v>3</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>20</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C50" t="str">
+        <f t="shared" si="12"/>
+        <v>GICS-LON rank(beta3m 1 3)</v>
+      </c>
+      <c r="D50" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" t="s">
+        <v>32</v>
+      </c>
+      <c r="J50" t="s">
+        <v>33</v>
+      </c>
+      <c r="K50">
+        <v>0.1</v>
+      </c>
+      <c r="L50">
+        <v>3</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="O50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P50" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <v>3</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>20</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C51" t="str">
+        <f t="shared" ref="C51" si="13">"GICS-"&amp;I51&amp;"("&amp;O51&amp;" "&amp;Q51&amp;" "&amp;R51&amp;")"</f>
+        <v>GICS-rank(rsi 1 3)</v>
+      </c>
+      <c r="D51" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J51" t="s">
+        <v>33</v>
+      </c>
+      <c r="K51">
+        <v>0.1</v>
+      </c>
+      <c r="L51">
+        <v>10</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="O51" t="s">
+        <v>48</v>
+      </c>
+      <c r="P51" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>20</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C52" t="str">
+        <f t="shared" ref="C52:C53" si="14">"GICS-"&amp;I52&amp;"("&amp;O52&amp;" "&amp;Q52&amp;" "&amp;R52&amp;")"</f>
+        <v>GICS-rank(rank 1 3)</v>
+      </c>
+      <c r="D52" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" t="s">
+        <v>32</v>
+      </c>
+      <c r="J52" t="s">
+        <v>33</v>
+      </c>
+      <c r="K52">
+        <v>0.1</v>
+      </c>
+      <c r="L52">
+        <v>10</v>
+      </c>
+      <c r="M52">
+        <v>4</v>
+      </c>
+      <c r="O52" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+      <c r="R52">
+        <v>3</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>20</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C53" t="str">
+        <f t="shared" si="14"/>
+        <v>GICS-rank(rsi -1 3)</v>
+      </c>
+      <c r="D53" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" t="s">
+        <v>32</v>
+      </c>
+      <c r="J53" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53">
+        <v>0.1</v>
+      </c>
+      <c r="L53">
+        <v>10</v>
+      </c>
+      <c r="M53">
+        <v>4</v>
+      </c>
+      <c r="O53" t="s">
+        <v>48</v>
+      </c>
+      <c r="P53" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q53">
+        <v>-1</v>
+      </c>
+      <c r="R53">
+        <v>3</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>20</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="9" t="str">
+        <f t="shared" ref="C54" si="15">"GICS-"&amp;I54&amp;"("&amp;O54&amp;" "&amp;Q54&amp;" "&amp;R54&amp;")"</f>
+        <v>GICS-rank(rank -1 3)</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L54" s="9">
+        <v>10</v>
+      </c>
+      <c r="M54" s="9">
+        <v>4</v>
+      </c>
+      <c r="O54" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R54" s="9">
+        <v>3</v>
+      </c>
+      <c r="S54" s="9">
+        <v>0</v>
+      </c>
+      <c r="T54" s="9">
+        <v>20</v>
+      </c>
+      <c r="U54" s="9">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECFFA95-FF41-422D-9768-8CAB2092B46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EE0F3A-5E7A-4494-BD04-5F3C38CCD076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21675" yWindow="1530" windowWidth="34875" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8760" yWindow="1965" windowWidth="34860" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="150">
   <si>
     <t>D</t>
   </si>
@@ -432,9 +432,6 @@
     <t>Næstbedst LON</t>
   </si>
   <si>
-    <t>næstbedst LON</t>
-  </si>
-  <si>
     <t>Godt gain, dårlig extension</t>
   </si>
   <si>
@@ -466,6 +463,15 @@
   </si>
   <si>
     <t>Longi.beta3m&gt;3</t>
+  </si>
+  <si>
+    <t>næstbedst LON, men kun halvt så god som beta-baseret</t>
+  </si>
+  <si>
+    <t>Ingen forbedring ved ændret sample</t>
+  </si>
+  <si>
+    <t>tickers_per_group her ingen betydning</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,12 +539,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -591,7 +591,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -606,8 +606,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -911,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1026,7 +1026,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
         <v>4</v>
       </c>
       <c r="N3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -1143,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="N4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="N5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>
@@ -1223,8 +1223,8 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>138</v>
+      <c r="V5" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -2522,7 +2522,7 @@
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
         <v>133</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="3:22" x14ac:dyDescent="0.25">
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="3:22" x14ac:dyDescent="0.25">
@@ -2792,7 +2792,7 @@
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E36" t="s">
         <v>133</v>
@@ -2816,7 +2816,7 @@
         <v>4</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O36" t="s">
         <v>27</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="3:22" x14ac:dyDescent="0.25">
@@ -2870,7 +2870,7 @@
         <v>4</v>
       </c>
       <c r="N37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O37" t="s">
         <v>27</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="3:22" x14ac:dyDescent="0.25">
@@ -2924,7 +2924,7 @@
         <v>4</v>
       </c>
       <c r="N38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O38" t="s">
         <v>27</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="3:22" x14ac:dyDescent="0.25">
@@ -2957,7 +2957,7 @@
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E39" t="s">
         <v>133</v>
@@ -2981,7 +2981,7 @@
         <v>4</v>
       </c>
       <c r="N39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O39" t="s">
         <v>27</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.25">
@@ -3014,7 +3014,7 @@
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
@@ -3038,7 +3038,7 @@
         <v>4</v>
       </c>
       <c r="N40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" t="s">
         <v>27</v>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.25">
@@ -3116,58 +3116,58 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="3:22" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="10" t="str">
+    <row r="42" spans="3:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="11" t="str">
         <f t="shared" ref="C42:C43" si="10">"GICS-LON " &amp;I42&amp;"("&amp;O42&amp;" "&amp;Q42&amp;" "&amp;R42&amp;")"</f>
         <v>GICS-LON rank(beta3m 1 3)</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" s="10" t="s">
+      <c r="D42" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" s="10" t="s">
+      <c r="F42" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K42" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="L42" s="10">
+      <c r="K42" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="11">
         <v>5</v>
       </c>
-      <c r="M42" s="10">
-        <v>4</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="P42" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42" s="10">
-        <v>1</v>
-      </c>
-      <c r="R42" s="10">
-        <v>3</v>
-      </c>
-      <c r="S42" s="10">
-        <v>0</v>
-      </c>
-      <c r="T42" s="10">
-        <v>20</v>
-      </c>
-      <c r="U42" s="10">
-        <v>0</v>
-      </c>
-      <c r="V42" s="10" t="s">
-        <v>138</v>
+      <c r="M42" s="11">
+        <v>4</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42" s="11">
+        <v>1</v>
+      </c>
+      <c r="R42" s="11">
+        <v>3</v>
+      </c>
+      <c r="S42" s="11">
+        <v>0</v>
+      </c>
+      <c r="T42" s="11">
+        <v>20</v>
+      </c>
+      <c r="U42" s="11">
+        <v>0</v>
+      </c>
+      <c r="V42" s="11" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="3:22" x14ac:dyDescent="0.25">
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="3:22" x14ac:dyDescent="0.25">
@@ -3674,7 +3674,7 @@
         <v>GICS-rank(rank 1 3)</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="3:22" x14ac:dyDescent="0.25">
@@ -3773,16 +3773,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C54" s="9" t="str">
-        <f t="shared" ref="C54" si="15">"GICS-"&amp;I54&amp;"("&amp;O54&amp;" "&amp;Q54&amp;" "&amp;R54&amp;")"</f>
+        <f t="shared" ref="C54:C60" si="15">"GICS-"&amp;I54&amp;"("&amp;O54&amp;" "&amp;Q54&amp;" "&amp;R54&amp;")"</f>
         <v>GICS-rank(rank -1 3)</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>25</v>
@@ -3827,7 +3827,349 @@
         <v>0</v>
       </c>
       <c r="V54" t="s">
-        <v>138</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C55" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 1)</v>
+      </c>
+      <c r="D55" t="s">
+        <v>148</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>26</v>
+      </c>
+      <c r="I55" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" t="s">
+        <v>28</v>
+      </c>
+      <c r="K55">
+        <v>0.1</v>
+      </c>
+      <c r="L55">
+        <v>10</v>
+      </c>
+      <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55" t="s">
+        <v>145</v>
+      </c>
+      <c r="O55" t="s">
+        <v>27</v>
+      </c>
+      <c r="P55" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>20</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C56" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 5)</v>
+      </c>
+      <c r="D56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" t="s">
+        <v>28</v>
+      </c>
+      <c r="K56">
+        <v>0.1</v>
+      </c>
+      <c r="L56">
+        <v>10</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56" t="s">
+        <v>145</v>
+      </c>
+      <c r="O56" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <v>5</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>20</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 10)</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K57" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L57" s="9">
+        <v>10</v>
+      </c>
+      <c r="M57" s="9">
+        <v>4</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>1</v>
+      </c>
+      <c r="R57" s="9">
+        <v>10</v>
+      </c>
+      <c r="S57" s="9">
+        <v>0</v>
+      </c>
+      <c r="T57" s="9">
+        <v>20</v>
+      </c>
+      <c r="U57" s="9">
+        <v>0</v>
+      </c>
+      <c r="V57" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C58" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D58" t="s">
+        <v>149</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" t="s">
+        <v>28</v>
+      </c>
+      <c r="K58">
+        <v>0.1</v>
+      </c>
+      <c r="L58">
+        <v>10</v>
+      </c>
+      <c r="M58">
+        <v>6</v>
+      </c>
+      <c r="N58" t="s">
+        <v>145</v>
+      </c>
+      <c r="O58" t="s">
+        <v>27</v>
+      </c>
+      <c r="P58" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <v>3</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>20</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C59" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D59" t="s">
+        <v>149</v>
+      </c>
+      <c r="E59" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" t="s">
+        <v>28</v>
+      </c>
+      <c r="K59">
+        <v>0.1</v>
+      </c>
+      <c r="L59">
+        <v>10</v>
+      </c>
+      <c r="M59">
+        <v>8</v>
+      </c>
+      <c r="N59" t="s">
+        <v>145</v>
+      </c>
+      <c r="O59" t="s">
+        <v>27</v>
+      </c>
+      <c r="P59" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59">
+        <v>1</v>
+      </c>
+      <c r="R59">
+        <v>3</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>20</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K60" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L60" s="9">
+        <v>10</v>
+      </c>
+      <c r="M60" s="9">
+        <v>10</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q60" s="9">
+        <v>1</v>
+      </c>
+      <c r="R60" s="9">
+        <v>3</v>
+      </c>
+      <c r="S60" s="9">
+        <v>0</v>
+      </c>
+      <c r="T60" s="9">
+        <v>20</v>
+      </c>
+      <c r="U60" s="9">
+        <v>0</v>
+      </c>
+      <c r="V60" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EE0F3A-5E7A-4494-BD04-5F3C38CCD076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EBBC08-A70F-4428-AAD2-C49811E25BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="1965" windowWidth="34860" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1965" windowWidth="46890" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="153">
   <si>
     <t>D</t>
   </si>
@@ -472,6 +472,15 @@
   </si>
   <si>
     <t>tickers_per_group her ingen betydning</t>
+  </si>
+  <si>
+    <t>rank, per1d</t>
+  </si>
+  <si>
+    <t>Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5</t>
+  </si>
+  <si>
+    <t>ingen forbedring</t>
   </si>
 </sst>
 </file>
@@ -490,6 +499,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -911,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3778,7 +3788,7 @@
     </row>
     <row r="54" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C54" s="9" t="str">
-        <f t="shared" ref="C54:C60" si="15">"GICS-"&amp;I54&amp;"("&amp;O54&amp;" "&amp;Q54&amp;" "&amp;R54&amp;")"</f>
+        <f t="shared" ref="C54:C61" si="15">"GICS-"&amp;I54&amp;"("&amp;O54&amp;" "&amp;Q54&amp;" "&amp;R54&amp;")"</f>
         <v>GICS-rank(rank -1 3)</v>
       </c>
       <c r="D54" s="9" t="s">
@@ -4170,6 +4180,402 @@
       </c>
       <c r="V60" s="9" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C61" t="str">
+        <f t="shared" si="15"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D61" t="s">
+        <v>152</v>
+      </c>
+      <c r="E61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" t="s">
+        <v>28</v>
+      </c>
+      <c r="K61">
+        <v>0.15</v>
+      </c>
+      <c r="L61">
+        <v>10</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61" t="s">
+        <v>134</v>
+      </c>
+      <c r="O61" t="s">
+        <v>27</v>
+      </c>
+      <c r="P61" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61">
+        <v>1</v>
+      </c>
+      <c r="R61">
+        <v>3</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>20</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C62" t="str">
+        <f t="shared" ref="C62:C63" si="16">"GICS-"&amp;I62&amp;"("&amp;O62&amp;" "&amp;Q62&amp;" "&amp;R62&amp;")"</f>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E62" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" t="s">
+        <v>28</v>
+      </c>
+      <c r="K62">
+        <v>0.15</v>
+      </c>
+      <c r="L62">
+        <v>10</v>
+      </c>
+      <c r="M62">
+        <v>4</v>
+      </c>
+      <c r="N62" t="s">
+        <v>145</v>
+      </c>
+      <c r="O62" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <v>3</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>20</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C63" t="str">
+        <f t="shared" si="16"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D63" t="s">
+        <v>152</v>
+      </c>
+      <c r="E63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" t="s">
+        <v>28</v>
+      </c>
+      <c r="K63">
+        <v>0.15</v>
+      </c>
+      <c r="L63">
+        <v>10</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63" t="s">
+        <v>134</v>
+      </c>
+      <c r="O63" t="s">
+        <v>27</v>
+      </c>
+      <c r="P63" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q63">
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <v>3</v>
+      </c>
+      <c r="S63">
+        <v>-20</v>
+      </c>
+      <c r="T63">
+        <v>20</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C64" t="str">
+        <f t="shared" ref="C64:C65" si="17">"GICS-"&amp;I64&amp;"("&amp;O64&amp;" "&amp;Q64&amp;" "&amp;R64&amp;")"</f>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E64" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" t="s">
+        <v>28</v>
+      </c>
+      <c r="K64">
+        <v>0.15</v>
+      </c>
+      <c r="L64">
+        <v>10</v>
+      </c>
+      <c r="M64">
+        <v>4</v>
+      </c>
+      <c r="N64" t="s">
+        <v>145</v>
+      </c>
+      <c r="O64" t="s">
+        <v>27</v>
+      </c>
+      <c r="P64" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64">
+        <v>3</v>
+      </c>
+      <c r="S64">
+        <v>-20</v>
+      </c>
+      <c r="T64">
+        <v>20</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C65" t="str">
+        <f t="shared" si="17"/>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I65" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" t="s">
+        <v>28</v>
+      </c>
+      <c r="K65">
+        <v>0.1</v>
+      </c>
+      <c r="L65">
+        <v>10</v>
+      </c>
+      <c r="M65">
+        <v>4</v>
+      </c>
+      <c r="O65" t="s">
+        <v>27</v>
+      </c>
+      <c r="P65" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>3</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>20</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C66" t="str">
+        <f t="shared" ref="C66" si="18">"GICS-"&amp;I66&amp;"("&amp;O66&amp;" "&amp;Q66&amp;" "&amp;R66&amp;")"</f>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D66" t="s">
+        <v>152</v>
+      </c>
+      <c r="E66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" t="s">
+        <v>26</v>
+      </c>
+      <c r="I66" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66">
+        <v>0.1</v>
+      </c>
+      <c r="L66">
+        <v>10</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66" t="s">
+        <v>151</v>
+      </c>
+      <c r="O66" t="s">
+        <v>27</v>
+      </c>
+      <c r="P66" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q66">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>3</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>20</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="9" t="str">
+        <f t="shared" ref="C67" si="19">"GICS-"&amp;I67&amp;"("&amp;O67&amp;" "&amp;Q67&amp;" "&amp;R67&amp;")"</f>
+        <v>GICS-beta3m(beta3m 1 3)</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K67" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="L67" s="9">
+        <v>10</v>
+      </c>
+      <c r="M67" s="9">
+        <v>5</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>1</v>
+      </c>
+      <c r="R67" s="9">
+        <v>3</v>
+      </c>
+      <c r="S67" s="9">
+        <v>0</v>
+      </c>
+      <c r="T67" s="9">
+        <v>20</v>
+      </c>
+      <c r="U67" s="9">
+        <v>0</v>
+      </c>
+      <c r="V67" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C1C5FE-2578-4B0B-8C9C-239F75726867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C092C235-07C0-4378-8C86-020F3BE6A2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1965" windowWidth="36840" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24630" yWindow="1680" windowWidth="31695" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="157">
   <si>
     <t>D</t>
   </si>
@@ -941,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1102,7 +1102,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E7" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
+        <f t="shared" ref="E3:E8" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
         <v>02 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F3" t="s">
@@ -1158,16 +1158,19 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
       <c r="C4">
-        <f t="shared" ref="C4:C67" si="1">C3+1</f>
+        <f t="shared" ref="C4:C6" si="1">C3+1</f>
         <v>3</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" si="0"/>
-        <v>03 GICS-rank (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" ref="E4" si="2">TEXT(C4,"00") &amp; " GICS-"&amp;K4&amp;" ("&amp;Q4&amp;IF(P4&lt;&gt;"","+ ","")&amp;P4&amp;")"</f>
+        <v>03 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1176,10 +1179,10 @@
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M4">
         <v>0.1</v>
@@ -1190,9 +1193,6 @@
       <c r="O4">
         <v>4</v>
       </c>
-      <c r="P4" t="s">
-        <v>143</v>
-      </c>
       <c r="Q4" t="s">
         <v>27</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>1</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
-        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;3)</v>
+        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1252,7 +1252,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
@@ -1275,8 +1275,8 @@
       <c r="W5">
         <v>0</v>
       </c>
-      <c r="X5" s="10" t="s">
-        <v>135</v>
+      <c r="X5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v>05 GICS-PdivMA20 (beta3m)</v>
+        <v>05 GICS-rank (beta3m+ Longi.beta3m&gt;3)</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -1298,10 +1298,10 @@
         <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M6">
         <v>0.1</v>
@@ -1312,6 +1312,9 @@
       <c r="O6">
         <v>4</v>
       </c>
+      <c r="P6" t="s">
+        <v>144</v>
+      </c>
       <c r="Q6" t="s">
         <v>27</v>
       </c>
@@ -1333,18 +1336,21 @@
       <c r="W6">
         <v>0</v>
       </c>
-      <c r="X6" t="s">
-        <v>29</v>
+      <c r="X6" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
       <c r="C7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C6:C68" si="3">C6+1</f>
         <v>6</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v>06 GICS-sh3m (beta3m)</v>
+        <v>06 GICS-PdivMA20 (beta3m)</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -1356,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="s">
         <v>28</v>
@@ -1397,20 +1403,24 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E8" t="s">
-        <v>35</v>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>07 GICS-sh3m (beta3m)</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -1451,11 +1461,11 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
         <v>36</v>
@@ -1464,10 +1474,10 @@
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M9">
         <v>0.1</v>
@@ -1505,11 +1515,11 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
         <v>36</v>
@@ -1518,10 +1528,10 @@
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M10">
         <v>0.1</v>
@@ -1559,11 +1569,11 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
@@ -1572,7 +1582,7 @@
         <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L11" t="s">
         <v>28</v>
@@ -1613,11 +1623,11 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -1626,7 +1636,7 @@
         <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L12" t="s">
         <v>28</v>
@@ -1667,11 +1677,11 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
         <v>36</v>
@@ -1680,7 +1690,7 @@
         <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L13" t="s">
         <v>28</v>
@@ -1721,11 +1731,11 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
         <v>36</v>
@@ -1734,10 +1744,10 @@
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <v>0.1</v>
@@ -1775,11 +1785,11 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
         <v>36</v>
@@ -1788,10 +1798,10 @@
         <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M15">
         <v>0.1</v>
@@ -1829,11 +1839,11 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G16" t="s">
         <v>36</v>
@@ -1842,7 +1852,7 @@
         <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L16" t="s">
         <v>28</v>
@@ -1883,11 +1893,11 @@
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
@@ -1896,10 +1906,10 @@
         <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M17">
         <v>0.1</v>
@@ -1937,11 +1947,11 @@
     </row>
     <row r="18" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
@@ -1950,10 +1960,10 @@
         <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M18">
         <v>0.1</v>
@@ -1991,21 +2001,20 @@
     </row>
     <row r="19" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="E19" t="str">
-        <f t="shared" ref="E19:E20" si="2">TEXT(C19,"00") &amp; " GICS-"&amp;K19&amp;" ("&amp;Q19&amp;IF(P19&lt;&gt;"","+ ","")&amp;P19&amp;")"</f>
-        <v>18 GICS-rsi (beta3m)</v>
+      <c r="E19" t="s">
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
         <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -2046,12 +2055,12 @@
     </row>
     <row r="20" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" si="2"/>
-        <v>19 GICS-spr100d (beta3m)</v>
+        <f t="shared" ref="E20:E21" si="4">TEXT(C20,"00") &amp; " GICS-"&amp;K20&amp;" ("&amp;Q20&amp;IF(P20&lt;&gt;"","+ ","")&amp;P20&amp;")"</f>
+        <v>19 GICS-rsi (beta3m)</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
@@ -2060,10 +2069,10 @@
         <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M20">
         <v>0.1</v>
@@ -2101,23 +2110,24 @@
     </row>
     <row r="21" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C21">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="E21" t="s">
-        <v>54</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="4"/>
+        <v>20 GICS-spr100d (beta3m)</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M21">
         <v>0.1</v>
@@ -2155,11 +2165,11 @@
     </row>
     <row r="22" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G22" t="s">
         <v>55</v>
@@ -2168,7 +2178,7 @@
         <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="L22" t="s">
         <v>28</v>
@@ -2209,11 +2219,11 @@
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
         <v>55</v>
@@ -2222,10 +2232,10 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M23">
         <v>0.1</v>
@@ -2263,27 +2273,23 @@
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="E24" t="str">
-        <f t="shared" ref="E24:E69" si="3">TEXT(C24,"00") &amp; " GICS-"&amp;K24&amp;" ("&amp;Q24&amp;IF(P24&lt;&gt;"","+ ","")&amp;P24&amp;")"</f>
-        <v>23 GICS-beta6m (beta6m)</v>
-      </c>
-      <c r="F24" t="s">
-        <v>127</v>
+      <c r="E24" t="s">
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M24">
         <v>0.1</v>
@@ -2295,7 +2301,7 @@
         <v>4</v>
       </c>
       <c r="Q24" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
         <v>28</v>
@@ -2321,12 +2327,12 @@
     </row>
     <row r="25" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="E25" t="str">
-        <f t="shared" si="3"/>
-        <v>24 GICS-beta3m (beta6m)</v>
+        <f t="shared" ref="E25:E70" si="5">TEXT(C25,"00") &amp; " GICS-"&amp;K25&amp;" ("&amp;Q25&amp;IF(P25&lt;&gt;"","+ ","")&amp;P25&amp;")"</f>
+        <v>24 GICS-beta6m (beta6m)</v>
       </c>
       <c r="F25" t="s">
         <v>127</v>
@@ -2338,7 +2344,7 @@
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="L25" t="s">
         <v>28</v>
@@ -2379,12 +2385,12 @@
     </row>
     <row r="26" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" si="3"/>
-        <v>25 GICS-beta6m (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>25 GICS-beta3m (beta6m)</v>
       </c>
       <c r="F26" t="s">
         <v>127</v>
@@ -2396,7 +2402,7 @@
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="L26" t="s">
         <v>28</v>
@@ -2411,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="Q26" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="R26" t="s">
         <v>28</v>
@@ -2437,15 +2443,15 @@
     </row>
     <row r="27" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="3"/>
-        <v>26 GICS-beta1m (beta1m)</v>
+        <f t="shared" si="5"/>
+        <v>26 GICS-beta6m (beta3m)</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -2454,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -2469,7 +2475,7 @@
         <v>4</v>
       </c>
       <c r="Q27" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
         <v>28</v>
@@ -2495,12 +2501,12 @@
     </row>
     <row r="28" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="E28" t="str">
-        <f t="shared" si="3"/>
-        <v>27 GICS-beta2m (beta2m)</v>
+        <f t="shared" si="5"/>
+        <v>27 GICS-beta1m (beta1m)</v>
       </c>
       <c r="F28" t="s">
         <v>130</v>
@@ -2512,7 +2518,7 @@
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2527,7 +2533,7 @@
         <v>4</v>
       </c>
       <c r="Q28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -2553,21 +2559,24 @@
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="E29" t="str">
-        <f t="shared" si="3"/>
-        <v>28 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>28 GICS-beta2m (beta2m)</v>
+      </c>
+      <c r="F29" t="s">
+        <v>130</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
         <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2576,16 +2585,13 @@
         <v>0.1</v>
       </c>
       <c r="N29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>4</v>
       </c>
-      <c r="P29" t="s">
-        <v>132</v>
-      </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="R29" t="s">
         <v>28</v>
@@ -2611,15 +2617,12 @@
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="3"/>
-        <v>29 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F30" t="s">
-        <v>133</v>
+        <f t="shared" si="5"/>
+        <v>29 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G30" t="s">
         <v>131</v>
@@ -2628,7 +2631,7 @@
         <v>26</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2672,15 +2675,15 @@
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" si="3"/>
-        <v>30 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>30 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F31" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G31" t="s">
         <v>131</v>
@@ -2689,10 +2692,10 @@
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M31">
         <v>0.1</v>
@@ -2728,17 +2731,20 @@
         <v>0</v>
       </c>
       <c r="X31" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="3"/>
-        <v>31 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>31 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F32" t="s">
+        <v>141</v>
       </c>
       <c r="G32" t="s">
         <v>131</v>
@@ -2747,10 +2753,10 @@
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M32">
         <v>0.1</v>
@@ -2786,17 +2792,17 @@
         <v>0</v>
       </c>
       <c r="X32" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" si="3"/>
-        <v>32 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>32 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G33" t="s">
         <v>131</v>
@@ -2805,7 +2811,7 @@
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -2849,12 +2855,12 @@
     </row>
     <row r="34" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" si="3"/>
-        <v>33 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>33 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G34" t="s">
         <v>131</v>
@@ -2863,10 +2869,10 @@
         <v>26</v>
       </c>
       <c r="K34" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M34">
         <v>0.1</v>
@@ -2907,12 +2913,12 @@
     </row>
     <row r="35" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="3"/>
-        <v>34 GICS-rank (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>34 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G35" t="s">
         <v>131</v>
@@ -2921,7 +2927,7 @@
         <v>26</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L35" t="s">
         <v>33</v>
@@ -2935,6 +2941,9 @@
       <c r="O35">
         <v>4</v>
       </c>
+      <c r="P35" t="s">
+        <v>132</v>
+      </c>
       <c r="Q35" t="s">
         <v>27</v>
       </c>
@@ -2957,20 +2966,17 @@
         <v>0</v>
       </c>
       <c r="X35" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="3"/>
-        <v>35 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
-      </c>
-      <c r="F36" t="s">
-        <v>141</v>
+        <f t="shared" si="5"/>
+        <v>35 GICS-rank (beta3m)</v>
       </c>
       <c r="G36" t="s">
         <v>131</v>
@@ -2993,9 +2999,6 @@
       <c r="O36">
         <v>4</v>
       </c>
-      <c r="P36" t="s">
-        <v>136</v>
-      </c>
       <c r="Q36" t="s">
         <v>27</v>
       </c>
@@ -3023,12 +3026,15 @@
     </row>
     <row r="37" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="3"/>
-        <v>36 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
+        <f t="shared" si="5"/>
+        <v>36 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
+      </c>
+      <c r="F37" t="s">
+        <v>141</v>
       </c>
       <c r="G37" t="s">
         <v>131</v>
@@ -3052,7 +3058,7 @@
         <v>4</v>
       </c>
       <c r="P37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
@@ -3081,12 +3087,12 @@
     </row>
     <row r="38" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="E38" t="str">
-        <f t="shared" si="3"/>
-        <v>37 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
+        <f t="shared" si="5"/>
+        <v>37 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
       </c>
       <c r="G38" t="s">
         <v>131</v>
@@ -3110,7 +3116,7 @@
         <v>4</v>
       </c>
       <c r="P38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -3139,15 +3145,12 @@
     </row>
     <row r="39" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="3"/>
-        <v>38 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
-      </c>
-      <c r="F39" t="s">
-        <v>141</v>
+        <f t="shared" si="5"/>
+        <v>38 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
       </c>
       <c r="G39" t="s">
         <v>131</v>
@@ -3171,7 +3174,7 @@
         <v>4</v>
       </c>
       <c r="P39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -3200,12 +3203,12 @@
     </row>
     <row r="40" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="3"/>
-        <v>39 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>39 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
       </c>
       <c r="F40" t="s">
         <v>141</v>
@@ -3232,7 +3235,7 @@
         <v>4</v>
       </c>
       <c r="P40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -3261,12 +3264,15 @@
     </row>
     <row r="41" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="3"/>
-        <v>40 GICS-PdivMA20 (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>40 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
+      </c>
+      <c r="F41" t="s">
+        <v>141</v>
       </c>
       <c r="G41" t="s">
         <v>131</v>
@@ -3275,10 +3281,10 @@
         <v>26</v>
       </c>
       <c r="K41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L41" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M41">
         <v>0.1</v>
@@ -3289,6 +3295,9 @@
       <c r="O41">
         <v>4</v>
       </c>
+      <c r="P41" t="s">
+        <v>140</v>
+      </c>
       <c r="Q41" t="s">
         <v>27</v>
       </c>
@@ -3311,136 +3320,130 @@
         <v>0</v>
       </c>
       <c r="X41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="5"/>
+        <v>41 GICS-PdivMA20 (beta3m)</v>
+      </c>
+      <c r="G42" t="s">
+        <v>131</v>
+      </c>
+      <c r="H42" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" t="s">
+        <v>28</v>
+      </c>
+      <c r="M42">
+        <v>0.1</v>
+      </c>
+      <c r="N42">
+        <v>5</v>
+      </c>
+      <c r="O42">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" t="s">
+        <v>28</v>
+      </c>
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <v>3</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>20</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="11">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="E42" s="11" t="str">
-        <f t="shared" si="3"/>
-        <v>41 GICS-rank (beta3m)</v>
-      </c>
-      <c r="F42" s="11" t="s">
+    <row r="43" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="11">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="E43" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>42 GICS-rank (beta3m)</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G43" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" s="11" t="s">
+      <c r="H43" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L43" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="N42" s="11">
+      <c r="M43" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="N43" s="11">
         <v>5</v>
       </c>
-      <c r="O42" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q42" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="R42" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="S42" s="11">
-        <v>1</v>
-      </c>
-      <c r="T42" s="11">
-        <v>3</v>
-      </c>
-      <c r="U42" s="11">
-        <v>0</v>
-      </c>
-      <c r="V42" s="11">
-        <v>20</v>
-      </c>
-      <c r="W42" s="11">
-        <v>0</v>
-      </c>
-      <c r="X42" s="11" t="s">
+      <c r="O43" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="S43" s="11">
+        <v>1</v>
+      </c>
+      <c r="T43" s="11">
+        <v>3</v>
+      </c>
+      <c r="U43" s="11">
+        <v>0</v>
+      </c>
+      <c r="V43" s="11">
+        <v>20</v>
+      </c>
+      <c r="W43" s="11">
+        <v>0</v>
+      </c>
+      <c r="X43" s="11" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C43">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="E43" t="str">
-        <f t="shared" si="3"/>
-        <v>42 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F43" t="s">
-        <v>130</v>
-      </c>
-      <c r="G43" t="s">
-        <v>131</v>
-      </c>
-      <c r="H43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" t="s">
-        <v>33</v>
-      </c>
-      <c r="M43">
-        <v>0.1</v>
-      </c>
-      <c r="N43">
-        <v>5</v>
-      </c>
-      <c r="O43">
-        <v>4</v>
-      </c>
-      <c r="P43" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>31</v>
-      </c>
-      <c r="R43" t="s">
-        <v>28</v>
-      </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
-        <v>3</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>20</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="44" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" si="3"/>
-        <v>43 GICS-rank (PdivMA20)</v>
+        <f t="shared" si="5"/>
+        <v>43 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F44" t="s">
         <v>130</v>
@@ -3466,6 +3469,9 @@
       <c r="O44">
         <v>4</v>
       </c>
+      <c r="P44" t="s">
+        <v>132</v>
+      </c>
       <c r="Q44" t="s">
         <v>31</v>
       </c>
@@ -3493,12 +3499,12 @@
     </row>
     <row r="45" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="E45" t="str">
-        <f t="shared" si="3"/>
-        <v>44 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>44 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F45" t="s">
         <v>130</v>
@@ -3516,7 +3522,7 @@
         <v>33</v>
       </c>
       <c r="M45">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -3524,11 +3530,8 @@
       <c r="O45">
         <v>4</v>
       </c>
-      <c r="P45" t="s">
-        <v>132</v>
-      </c>
       <c r="Q45" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R45" t="s">
         <v>28</v>
@@ -3554,12 +3557,12 @@
     </row>
     <row r="46" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="E46" t="str">
-        <f t="shared" si="3"/>
-        <v>45 GICS-rank (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>45 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F46" t="s">
         <v>130</v>
@@ -3585,6 +3588,9 @@
       <c r="O46">
         <v>4</v>
       </c>
+      <c r="P46" t="s">
+        <v>132</v>
+      </c>
       <c r="Q46" t="s">
         <v>27</v>
       </c>
@@ -3612,12 +3618,12 @@
     </row>
     <row r="47" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="E47" t="str">
-        <f t="shared" si="3"/>
-        <v>46 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>46 GICS-rank (beta3m)</v>
       </c>
       <c r="F47" t="s">
         <v>130</v>
@@ -3635,19 +3641,16 @@
         <v>33</v>
       </c>
       <c r="M47">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>4</v>
       </c>
-      <c r="P47" t="s">
-        <v>132</v>
-      </c>
       <c r="Q47" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R47" t="s">
         <v>28</v>
@@ -3673,12 +3676,12 @@
     </row>
     <row r="48" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="E48" t="str">
-        <f t="shared" si="3"/>
-        <v>47 GICS-rank (PdivMA20)</v>
+        <f t="shared" si="5"/>
+        <v>47 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F48" t="s">
         <v>130</v>
@@ -3704,6 +3707,9 @@
       <c r="O48">
         <v>4</v>
       </c>
+      <c r="P48" t="s">
+        <v>132</v>
+      </c>
       <c r="Q48" t="s">
         <v>31</v>
       </c>
@@ -3731,12 +3737,12 @@
     </row>
     <row r="49" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="E49" t="str">
-        <f t="shared" si="3"/>
-        <v>48 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>48 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F49" t="s">
         <v>130</v>
@@ -3762,11 +3768,8 @@
       <c r="O49">
         <v>4</v>
       </c>
-      <c r="P49" t="s">
-        <v>132</v>
-      </c>
       <c r="Q49" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R49" t="s">
         <v>28</v>
@@ -3792,12 +3795,12 @@
     </row>
     <row r="50" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="E50" t="str">
-        <f t="shared" si="3"/>
-        <v>49 GICS-rank (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>49 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F50" t="s">
         <v>130</v>
@@ -3823,6 +3826,9 @@
       <c r="O50">
         <v>4</v>
       </c>
+      <c r="P50" t="s">
+        <v>132</v>
+      </c>
       <c r="Q50" t="s">
         <v>27</v>
       </c>
@@ -3850,18 +3856,18 @@
     </row>
     <row r="51" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" si="3"/>
-        <v>50 GICS-rank (rsi)</v>
+        <f t="shared" si="5"/>
+        <v>50 GICS-rank (beta3m)</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="H51" t="s">
         <v>26</v>
@@ -3876,13 +3882,13 @@
         <v>0.1</v>
       </c>
       <c r="N51">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>4</v>
       </c>
       <c r="Q51" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="R51" t="s">
         <v>28</v>
@@ -3903,20 +3909,20 @@
         <v>0</v>
       </c>
       <c r="X51" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" si="3"/>
-        <v>51 GICS-rank (rank)</v>
+        <f t="shared" si="5"/>
+        <v>51 GICS-rank (rsi)</v>
       </c>
       <c r="F52" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -3940,10 +3946,10 @@
         <v>4</v>
       </c>
       <c r="Q52" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="R52" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S52">
         <v>1</v>
@@ -3966,15 +3972,15 @@
     </row>
     <row r="53" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="E53" t="str">
-        <f t="shared" si="3"/>
-        <v>52 GICS-rank (rsi)</v>
+        <f t="shared" si="5"/>
+        <v>52 GICS-rank (rank)</v>
       </c>
       <c r="F53" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -3998,13 +4004,13 @@
         <v>4</v>
       </c>
       <c r="Q53" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="R53" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S53">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T53">
         <v>3</v>
@@ -4022,119 +4028,116 @@
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="9">
-        <f t="shared" si="1"/>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
-      <c r="E54" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>53 GICS-rank (rank)</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G54" s="9" t="s">
+      <c r="E54" t="str">
+        <f t="shared" si="5"/>
+        <v>53 GICS-rank (rsi)</v>
+      </c>
+      <c r="F54" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" t="s">
         <v>25</v>
       </c>
-      <c r="H54" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K54" s="9" t="s">
+      <c r="H54" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54" t="s">
         <v>32</v>
       </c>
-      <c r="L54" s="9" t="s">
+      <c r="L54" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N54" s="9">
+      <c r="M54">
+        <v>0.1</v>
+      </c>
+      <c r="N54">
         <v>10</v>
       </c>
-      <c r="O54" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q54" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R54" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="S54" s="9">
+      <c r="O54">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>48</v>
+      </c>
+      <c r="R54" t="s">
+        <v>28</v>
+      </c>
+      <c r="S54">
         <v>-1</v>
       </c>
-      <c r="T54" s="9">
-        <v>3</v>
-      </c>
-      <c r="U54" s="9">
-        <v>0</v>
-      </c>
-      <c r="V54" s="9">
-        <v>20</v>
-      </c>
-      <c r="W54" s="9">
+      <c r="T54">
+        <v>3</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>20</v>
+      </c>
+      <c r="W54">
         <v>0</v>
       </c>
       <c r="X54" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C55">
-        <f t="shared" si="1"/>
+    <row r="55" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="9">
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="E55" t="str">
-        <f t="shared" si="3"/>
-        <v>54 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F55" t="s">
-        <v>146</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="E55" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>54 GICS-rank (rank)</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H55" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" t="s">
-        <v>27</v>
-      </c>
-      <c r="L55" t="s">
-        <v>28</v>
-      </c>
-      <c r="M55">
-        <v>0.1</v>
-      </c>
-      <c r="N55">
+      <c r="H55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N55" s="9">
         <v>10</v>
       </c>
-      <c r="O55">
-        <v>4</v>
-      </c>
-      <c r="P55" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>27</v>
-      </c>
-      <c r="R55" t="s">
-        <v>28</v>
-      </c>
-      <c r="S55">
-        <v>1</v>
-      </c>
-      <c r="T55">
-        <v>1</v>
-      </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
-      <c r="V55">
-        <v>20</v>
-      </c>
-      <c r="W55">
+      <c r="O55" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R55" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S55" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T55" s="9">
+        <v>3</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0</v>
+      </c>
+      <c r="V55" s="9">
+        <v>20</v>
+      </c>
+      <c r="W55" s="9">
         <v>0</v>
       </c>
       <c r="X55" t="s">
@@ -4143,11 +4146,11 @@
     </row>
     <row r="56" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="E56" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>55 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F56" t="s">
@@ -4187,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="T56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -4202,135 +4205,135 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="9">
-        <f t="shared" si="1"/>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="E57" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="E57" t="str">
+        <f t="shared" si="5"/>
         <v>56 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" t="s">
         <v>146</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" t="s">
         <v>25</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M57" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N57" s="9">
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57">
+        <v>0.1</v>
+      </c>
+      <c r="N57">
         <v>10</v>
       </c>
-      <c r="O57" s="9">
-        <v>4</v>
-      </c>
-      <c r="P57" s="9" t="s">
+      <c r="O57">
+        <v>4</v>
+      </c>
+      <c r="P57" t="s">
         <v>143</v>
       </c>
-      <c r="Q57" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S57" s="9">
-        <v>1</v>
-      </c>
-      <c r="T57" s="9">
+      <c r="Q57" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" t="s">
+        <v>28</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <v>5</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>20</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="9">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="E58" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>57 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N58" s="9">
         <v>10</v>
       </c>
-      <c r="U57" s="9">
-        <v>0</v>
-      </c>
-      <c r="V57" s="9">
-        <v>20</v>
-      </c>
-      <c r="W57" s="9">
-        <v>0</v>
-      </c>
-      <c r="X57" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C58">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="E58" t="str">
-        <f t="shared" si="3"/>
-        <v>57 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F58" t="s">
-        <v>147</v>
-      </c>
-      <c r="G58" t="s">
-        <v>25</v>
-      </c>
-      <c r="H58" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" t="s">
-        <v>27</v>
-      </c>
-      <c r="L58" t="s">
-        <v>28</v>
-      </c>
-      <c r="M58">
-        <v>0.1</v>
-      </c>
-      <c r="N58">
+      <c r="O58" s="9">
+        <v>4</v>
+      </c>
+      <c r="P58" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q58" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S58" s="9">
+        <v>1</v>
+      </c>
+      <c r="T58" s="9">
         <v>10</v>
       </c>
-      <c r="O58">
-        <v>6</v>
-      </c>
-      <c r="P58" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>27</v>
-      </c>
-      <c r="R58" t="s">
-        <v>28</v>
-      </c>
-      <c r="S58">
-        <v>1</v>
-      </c>
-      <c r="T58">
-        <v>3</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>20</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58" t="s">
+      <c r="U58" s="9">
+        <v>0</v>
+      </c>
+      <c r="V58" s="9">
+        <v>20</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="59" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>58 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F59" t="s">
@@ -4355,7 +4358,7 @@
         <v>10</v>
       </c>
       <c r="O59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P59" t="s">
         <v>143</v>
@@ -4385,136 +4388,136 @@
         <v>135</v>
       </c>
     </row>
-    <row r="60" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="9">
-        <f t="shared" si="1"/>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="E60" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="E60" t="str">
+        <f t="shared" si="5"/>
         <v>59 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" t="s">
         <v>147</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" t="s">
         <v>25</v>
       </c>
-      <c r="H60" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M60" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N60" s="9">
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60">
+        <v>0.1</v>
+      </c>
+      <c r="N60">
         <v>10</v>
       </c>
-      <c r="O60" s="9">
+      <c r="O60">
+        <v>8</v>
+      </c>
+      <c r="P60" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" t="s">
+        <v>28</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <v>3</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>20</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="9">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E61" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>60 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N61" s="9">
         <v>10</v>
       </c>
-      <c r="P60" s="9" t="s">
+      <c r="O61" s="9">
+        <v>10</v>
+      </c>
+      <c r="P61" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Q60" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R60" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S60" s="9">
-        <v>1</v>
-      </c>
-      <c r="T60" s="9">
-        <v>3</v>
-      </c>
-      <c r="U60" s="9">
-        <v>0</v>
-      </c>
-      <c r="V60" s="9">
-        <v>20</v>
-      </c>
-      <c r="W60" s="9">
-        <v>0</v>
-      </c>
-      <c r="X60" s="9" t="s">
+      <c r="Q61" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S61" s="9">
+        <v>1</v>
+      </c>
+      <c r="T61" s="9">
+        <v>3</v>
+      </c>
+      <c r="U61" s="9">
+        <v>0</v>
+      </c>
+      <c r="V61" s="9">
+        <v>20</v>
+      </c>
+      <c r="W61" s="9">
+        <v>0</v>
+      </c>
+      <c r="X61" s="9" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C61">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="E61" t="str">
-        <f t="shared" si="3"/>
-        <v>60 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F61" t="s">
-        <v>150</v>
-      </c>
-      <c r="G61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H61" t="s">
-        <v>26</v>
-      </c>
-      <c r="K61" t="s">
-        <v>27</v>
-      </c>
-      <c r="L61" t="s">
-        <v>28</v>
-      </c>
-      <c r="M61">
-        <v>0.15</v>
-      </c>
-      <c r="N61">
-        <v>10</v>
-      </c>
-      <c r="O61">
-        <v>4</v>
-      </c>
-      <c r="P61" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>27</v>
-      </c>
-      <c r="R61" t="s">
-        <v>28</v>
-      </c>
-      <c r="S61">
-        <v>1</v>
-      </c>
-      <c r="T61">
-        <v>3</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>20</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="62" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>61</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" si="3"/>
-        <v>61 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="5"/>
+        <v>61 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F62" t="s">
         <v>150</v>
@@ -4541,7 +4544,7 @@
         <v>4</v>
       </c>
       <c r="P62" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
@@ -4570,12 +4573,12 @@
     </row>
     <row r="63" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>62</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="3"/>
-        <v>62 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <f t="shared" si="5"/>
+        <v>62 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F63" t="s">
         <v>150</v>
@@ -4602,7 +4605,7 @@
         <v>4</v>
       </c>
       <c r="P63" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -4617,7 +4620,7 @@
         <v>3</v>
       </c>
       <c r="U63">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="V63">
         <v>20</v>
@@ -4631,12 +4634,12 @@
     </row>
     <row r="64" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
       <c r="E64" t="str">
-        <f t="shared" si="3"/>
-        <v>63 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="5"/>
+        <v>63 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F64" t="s">
         <v>150</v>
@@ -4663,7 +4666,7 @@
         <v>4</v>
       </c>
       <c r="P64" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -4692,12 +4695,12 @@
     </row>
     <row r="65" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="E65" t="str">
-        <f t="shared" si="3"/>
-        <v>64 GICS-beta3m (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>64 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F65" t="s">
         <v>150</v>
@@ -4715,7 +4718,7 @@
         <v>28</v>
       </c>
       <c r="M65">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N65">
         <v>10</v>
@@ -4723,6 +4726,9 @@
       <c r="O65">
         <v>4</v>
       </c>
+      <c r="P65" t="s">
+        <v>143</v>
+      </c>
       <c r="Q65" t="s">
         <v>27</v>
       </c>
@@ -4736,7 +4742,7 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V65">
         <v>20</v>
@@ -4750,12 +4756,12 @@
     </row>
     <row r="66" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="E66" t="str">
-        <f t="shared" si="3"/>
-        <v>65 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="5"/>
+        <v>65 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F66" t="s">
         <v>150</v>
@@ -4781,9 +4787,6 @@
       <c r="O66">
         <v>4</v>
       </c>
-      <c r="P66" t="s">
-        <v>149</v>
-      </c>
       <c r="Q66" t="s">
         <v>27</v>
       </c>
@@ -4809,129 +4812,126 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="9">
-        <f t="shared" si="1"/>
+    <row r="67" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <f t="shared" si="3"/>
         <v>66</v>
       </c>
-      <c r="E67" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="E67" t="str">
+        <f t="shared" si="5"/>
         <v>66 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" t="s">
         <v>150</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" t="s">
         <v>25</v>
       </c>
-      <c r="H67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M67" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N67" s="9">
+      <c r="H67" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67" t="s">
+        <v>27</v>
+      </c>
+      <c r="L67" t="s">
+        <v>28</v>
+      </c>
+      <c r="M67">
+        <v>0.1</v>
+      </c>
+      <c r="N67">
         <v>10</v>
       </c>
-      <c r="O67" s="9">
+      <c r="O67">
+        <v>4</v>
+      </c>
+      <c r="P67" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" t="s">
+        <v>28</v>
+      </c>
+      <c r="S67">
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <v>3</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>20</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="9">
+        <f t="shared" si="3"/>
+        <v>67</v>
+      </c>
+      <c r="E68" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>67 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M68" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N68" s="9">
+        <v>10</v>
+      </c>
+      <c r="O68" s="9">
         <v>5</v>
       </c>
-      <c r="P67" s="9" t="s">
+      <c r="P68" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="Q67" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R67" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S67" s="9">
-        <v>1</v>
-      </c>
-      <c r="T67" s="9">
-        <v>3</v>
-      </c>
-      <c r="U67" s="9">
-        <v>0</v>
-      </c>
-      <c r="V67" s="9">
-        <v>20</v>
-      </c>
-      <c r="W67" s="9">
-        <v>0</v>
-      </c>
-      <c r="X67" s="9" t="s">
+      <c r="Q68" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S68" s="9">
+        <v>1</v>
+      </c>
+      <c r="T68" s="9">
+        <v>3</v>
+      </c>
+      <c r="U68" s="9">
+        <v>0</v>
+      </c>
+      <c r="V68" s="9">
+        <v>20</v>
+      </c>
+      <c r="W68" s="9">
+        <v>0</v>
+      </c>
+      <c r="X68" s="9" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="68" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C68">
-        <f>C67+1</f>
-        <v>67</v>
-      </c>
-      <c r="D68" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" t="str">
-        <f t="shared" si="3"/>
-        <v>67 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F68" t="s">
-        <v>156</v>
-      </c>
-      <c r="G68" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="L68" t="s">
-        <v>28</v>
-      </c>
-      <c r="M68">
-        <v>0.1</v>
-      </c>
-      <c r="N68">
-        <v>10</v>
-      </c>
-      <c r="O68">
-        <v>4</v>
-      </c>
-      <c r="P68" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>27</v>
-      </c>
-      <c r="R68" t="s">
-        <v>28</v>
-      </c>
-      <c r="S68">
-        <v>1</v>
-      </c>
-      <c r="T68">
-        <v>3</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>20</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="69" spans="3:24" x14ac:dyDescent="0.25">
@@ -4943,8 +4943,8 @@
         <v>153</v>
       </c>
       <c r="E69" t="str">
-        <f t="shared" si="3"/>
-        <v>68 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="5"/>
+        <v>68 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F69" t="s">
         <v>156</v>
@@ -4956,7 +4956,7 @@
         <v>26</v>
       </c>
       <c r="K69" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L69" t="s">
         <v>28</v>
@@ -5007,8 +5007,8 @@
         <v>153</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" ref="E70:E71" si="4">TEXT(C70,"00") &amp; " GICS-"&amp;K70&amp;" ("&amp;Q70&amp;IF(P70&lt;&gt;"","+ ","")&amp;P70&amp;")"</f>
-        <v>69 GICS-beta2m (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>69 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F70" t="s">
         <v>156</v>
@@ -5020,7 +5020,7 @@
         <v>26</v>
       </c>
       <c r="K70" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L70" t="s">
         <v>28</v>
@@ -5034,7 +5034,9 @@
       <c r="O70">
         <v>4</v>
       </c>
-      <c r="P70" s="12"/>
+      <c r="P70" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="Q70" t="s">
         <v>27</v>
       </c>
@@ -5069,8 +5071,8 @@
         <v>153</v>
       </c>
       <c r="E71" t="str">
-        <f t="shared" si="4"/>
-        <v>70 GICS-beta1m (beta3m)</v>
+        <f t="shared" ref="E71:E72" si="6">TEXT(C71,"00") &amp; " GICS-"&amp;K71&amp;" ("&amp;Q71&amp;IF(P71&lt;&gt;"","+ ","")&amp;P71&amp;")"</f>
+        <v>70 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F71" t="s">
         <v>156</v>
@@ -5082,7 +5084,7 @@
         <v>26</v>
       </c>
       <c r="K71" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L71" t="s">
         <v>28</v>
@@ -5131,8 +5133,8 @@
         <v>153</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" ref="E72" si="5">TEXT(C72,"00") &amp; " GICS-"&amp;K72&amp;" ("&amp;Q72&amp;IF(P72&lt;&gt;"","+ ","")&amp;P72&amp;")"</f>
-        <v>71 GICS-beta2m (beta3m)</v>
+        <f t="shared" si="6"/>
+        <v>71 GICS-beta1m (beta3m)</v>
       </c>
       <c r="F72" t="s">
         <v>156</v>
@@ -5143,8 +5145,8 @@
       <c r="H72" t="s">
         <v>26</v>
       </c>
-      <c r="K72" t="s">
-        <v>129</v>
+      <c r="K72" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="L72" t="s">
         <v>28</v>
@@ -5155,9 +5157,10 @@
       <c r="N72">
         <v>10</v>
       </c>
-      <c r="O72" s="12">
-        <v>5</v>
-      </c>
+      <c r="O72">
+        <v>4</v>
+      </c>
+      <c r="P72" s="12"/>
       <c r="Q72" t="s">
         <v>27</v>
       </c>
@@ -5185,18 +5188,18 @@
     </row>
     <row r="73" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C73">
-        <f t="shared" ref="C73:C74" si="6">C72+1</f>
+        <f>C72+1</f>
         <v>72</v>
       </c>
       <c r="D73" t="s">
         <v>153</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" ref="E73:E74" si="7">TEXT(C73,"00") &amp; " GICS-"&amp;K73&amp;" ("&amp;Q73&amp;IF(P73&lt;&gt;"","+ ","")&amp;P73&amp;")"</f>
+        <f t="shared" ref="E73" si="7">TEXT(C73,"00") &amp; " GICS-"&amp;K73&amp;" ("&amp;Q73&amp;IF(P73&lt;&gt;"","+ ","")&amp;P73&amp;")"</f>
         <v>72 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -5216,8 +5219,8 @@
       <c r="N73">
         <v>10</v>
       </c>
-      <c r="O73">
-        <v>4</v>
+      <c r="O73" s="12">
+        <v>5</v>
       </c>
       <c r="Q73" t="s">
         <v>27</v>
@@ -5225,8 +5228,8 @@
       <c r="R73" t="s">
         <v>28</v>
       </c>
-      <c r="S73" s="12">
-        <v>3</v>
+      <c r="S73">
+        <v>1</v>
       </c>
       <c r="T73">
         <v>3</v>
@@ -5244,64 +5247,125 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="9">
-        <f t="shared" si="6"/>
+    <row r="74" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <f t="shared" ref="C74:C75" si="8">C73+1</f>
         <v>73</v>
       </c>
-      <c r="D74" s="9" t="s">
+      <c r="D74" t="s">
         <v>153</v>
       </c>
-      <c r="E74" s="9" t="str">
-        <f t="shared" si="7"/>
+      <c r="E74" t="str">
+        <f t="shared" ref="E74:E75" si="9">TEXT(C74,"00") &amp; " GICS-"&amp;K74&amp;" ("&amp;Q74&amp;IF(P74&lt;&gt;"","+ ","")&amp;P74&amp;")"</f>
         <v>73 GICS-beta2m (beta3m)</v>
       </c>
-      <c r="F74" s="9" t="s">
+      <c r="F74" t="s">
         <v>155</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G74" t="s">
         <v>25</v>
       </c>
-      <c r="H74" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K74" s="9" t="s">
+      <c r="H74" t="s">
+        <v>26</v>
+      </c>
+      <c r="K74" t="s">
         <v>129</v>
       </c>
-      <c r="L74" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N74" s="9">
+      <c r="L74" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74">
+        <v>0.1</v>
+      </c>
+      <c r="N74">
         <v>10</v>
       </c>
-      <c r="O74" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q74" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R74" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S74" s="13" t="s">
+      <c r="O74">
+        <v>4</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>27</v>
+      </c>
+      <c r="R74" t="s">
+        <v>28</v>
+      </c>
+      <c r="S74" s="12">
+        <v>3</v>
+      </c>
+      <c r="T74">
+        <v>3</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>20</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="75" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="9">
+        <f t="shared" si="8"/>
+        <v>74</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E75" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>74 GICS-beta2m (beta3m)</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N75" s="9">
+        <v>10</v>
+      </c>
+      <c r="O75" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R75" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S75" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="T74" s="9">
-        <v>3</v>
-      </c>
-      <c r="U74" s="9">
-        <v>0</v>
-      </c>
-      <c r="V74" s="9">
-        <v>20</v>
-      </c>
-      <c r="W74" s="9">
-        <v>0</v>
-      </c>
-      <c r="X74" s="9" t="s">
+      <c r="T75" s="9">
+        <v>3</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0</v>
+      </c>
+      <c r="V75" s="9">
+        <v>20</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9" t="s">
         <v>135</v>
       </c>
     </row>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C092C235-07C0-4378-8C86-020F3BE6A2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CD735E-896D-4A99-9D67-FFAF630AF239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24630" yWindow="1680" windowWidth="31695" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21900" windowHeight="15495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="158">
   <si>
     <t>D</t>
   </si>
@@ -493,6 +493,9 @@
   </si>
   <si>
     <t>Næsten som 02</t>
+  </si>
+  <si>
+    <t>Basis</t>
   </si>
 </sst>
 </file>
@@ -1037,6 +1040,9 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" t="s">
+        <v>157</v>
+      </c>
       <c r="E2" t="str">
         <f>TEXT(C2,"00") &amp; " GICS-"&amp;K2&amp;" ("&amp;Q2&amp;IF(P2&lt;&gt;"","+ ","")&amp;P2&amp;")"</f>
         <v>01 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
@@ -1090,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -1100,6 +1106,9 @@
       <c r="C3">
         <f>C2+1</f>
         <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>157</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E8" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
@@ -1345,7 +1354,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C6:C68" si="3">C6+1</f>
+        <f t="shared" ref="C7:C68" si="3">C6+1</f>
         <v>6</v>
       </c>
       <c r="E7" t="str">

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CD735E-896D-4A99-9D67-FFAF630AF239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3400EC81-26C1-43BA-A31A-D7BF2B1BA3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21900" windowHeight="15495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29505" yWindow="1485" windowWidth="35205" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="160">
   <si>
     <t>D</t>
   </si>
@@ -496,6 +496,12 @@
   </si>
   <si>
     <t>Basis</t>
+  </si>
+  <si>
+    <t>Stamdata.Sector2</t>
+  </si>
+  <si>
+    <t>Rimelig</t>
   </si>
 </sst>
 </file>
@@ -944,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1048,7 +1054,7 @@
         <v>01 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -1111,11 +1117,11 @@
         <v>157</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E8" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
+        <f t="shared" ref="E3:E10" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
         <v>02 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -1167,9 +1173,6 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
       <c r="C4">
         <f t="shared" ref="C4:C6" si="1">C3+1</f>
         <v>3</v>
@@ -1179,7 +1182,7 @@
         <v>03 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1350,11 +1353,8 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7">
-        <f t="shared" ref="C7:C68" si="3">C6+1</f>
+        <f t="shared" ref="C7:C70" si="3">C6+1</f>
         <v>6</v>
       </c>
       <c r="E7" t="str">
@@ -1411,6 +1411,9 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
       <c r="C8">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -1420,7 +1423,7 @@
         <v>07 GICS-sh3m (beta3m)</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -1473,17 +1476,21 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E9" t="s">
-        <v>35</v>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>08 GICS-quot1020 (beta3m)</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
@@ -1523,24 +1530,31 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
       <c r="C10">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E10" t="s">
-        <v>37</v>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>09 GICS-quot2050 (beta3m)</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M10">
         <v>0.1</v>
@@ -1582,7 +1596,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
@@ -1591,7 +1605,7 @@
         <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
         <v>28</v>
@@ -1636,7 +1650,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -1645,10 +1659,10 @@
         <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M12">
         <v>0.1</v>
@@ -1690,7 +1704,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
         <v>36</v>
@@ -1699,7 +1713,7 @@
         <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L13" t="s">
         <v>28</v>
@@ -1744,7 +1758,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
         <v>36</v>
@@ -1753,7 +1767,7 @@
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
         <v>28</v>
@@ -1798,7 +1812,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
         <v>36</v>
@@ -1807,10 +1821,10 @@
         <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M15">
         <v>0.1</v>
@@ -1852,7 +1866,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
         <v>36</v>
@@ -1861,7 +1875,7 @@
         <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
         <v>28</v>
@@ -1906,7 +1920,7 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
@@ -1915,10 +1929,10 @@
         <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M17">
         <v>0.1</v>
@@ -1960,7 +1974,7 @@
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
@@ -1969,10 +1983,10 @@
         <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M18">
         <v>0.1</v>
@@ -2014,7 +2028,7 @@
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
         <v>36</v>
@@ -2023,7 +2037,7 @@
         <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -2067,21 +2081,20 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="E20" t="str">
-        <f t="shared" ref="E20:E21" si="4">TEXT(C20,"00") &amp; " GICS-"&amp;K20&amp;" ("&amp;Q20&amp;IF(P20&lt;&gt;"","+ ","")&amp;P20&amp;")"</f>
-        <v>19 GICS-rsi (beta3m)</v>
+      <c r="E20" t="s">
+        <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s">
         <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M20">
         <v>0.1</v>
@@ -2122,21 +2135,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="E21" t="str">
-        <f t="shared" si="4"/>
-        <v>20 GICS-spr100d (beta3m)</v>
+      <c r="E21" t="s">
+        <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M21">
         <v>0.1</v>
@@ -2177,17 +2189,18 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="E22" t="s">
-        <v>54</v>
+      <c r="E22" t="str">
+        <f t="shared" ref="E22:E23" si="4">TEXT(C22,"00") &amp; " GICS-"&amp;K22&amp;" ("&amp;Q22&amp;IF(P22&lt;&gt;"","+ ","")&amp;P22&amp;")"</f>
+        <v>21 GICS-rsi (beta3m)</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H22" t="s">
         <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L22" t="s">
         <v>28</v>
@@ -2231,20 +2244,21 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="E23" t="s">
-        <v>56</v>
+      <c r="E23" t="str">
+        <f t="shared" si="4"/>
+        <v>22 GICS-spr100d (beta3m)</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s">
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M23">
         <v>0.1</v>
@@ -2286,7 +2300,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G24" t="s">
         <v>55</v>
@@ -2295,10 +2309,10 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M24">
         <v>0.1</v>
@@ -2339,21 +2353,17 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="E25" t="str">
-        <f t="shared" ref="E25:E70" si="5">TEXT(C25,"00") &amp; " GICS-"&amp;K25&amp;" ("&amp;Q25&amp;IF(P25&lt;&gt;"","+ ","")&amp;P25&amp;")"</f>
-        <v>24 GICS-beta6m (beta6m)</v>
-      </c>
-      <c r="F25" t="s">
-        <v>127</v>
+      <c r="E25" t="s">
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H25" t="s">
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="L25" t="s">
         <v>28</v>
@@ -2368,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="Q25" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>28</v>
@@ -2397,24 +2407,20 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="E26" t="str">
-        <f t="shared" si="5"/>
-        <v>25 GICS-beta3m (beta6m)</v>
-      </c>
-      <c r="F26" t="s">
-        <v>127</v>
+      <c r="E26" t="s">
+        <v>57</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="L26" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M26">
         <v>0.1</v>
@@ -2426,7 +2432,7 @@
         <v>4</v>
       </c>
       <c r="Q26" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
         <v>28</v>
@@ -2456,8 +2462,8 @@
         <v>26</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="5"/>
-        <v>26 GICS-beta6m (beta3m)</v>
+        <f t="shared" ref="E27:E72" si="5">TEXT(C27,"00") &amp; " GICS-"&amp;K27&amp;" ("&amp;Q27&amp;IF(P27&lt;&gt;"","+ ","")&amp;P27&amp;")"</f>
+        <v>26 GICS-beta6m (beta6m)</v>
       </c>
       <c r="F27" t="s">
         <v>127</v>
@@ -2484,7 +2490,7 @@
         <v>4</v>
       </c>
       <c r="Q27" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="R27" t="s">
         <v>28</v>
@@ -2515,10 +2521,10 @@
       </c>
       <c r="E28" t="str">
         <f t="shared" si="5"/>
-        <v>27 GICS-beta1m (beta1m)</v>
+        <v>27 GICS-beta3m (beta6m)</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
@@ -2527,7 +2533,7 @@
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2542,7 +2548,7 @@
         <v>4</v>
       </c>
       <c r="Q28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -2573,10 +2579,10 @@
       </c>
       <c r="E29" t="str">
         <f t="shared" si="5"/>
-        <v>28 GICS-beta2m (beta2m)</v>
+        <v>28 GICS-beta6m (beta3m)</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
@@ -2585,7 +2591,7 @@
         <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2600,7 +2606,7 @@
         <v>4</v>
       </c>
       <c r="Q29" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
         <v>28</v>
@@ -2631,16 +2637,19 @@
       </c>
       <c r="E30" t="str">
         <f t="shared" si="5"/>
-        <v>29 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>29 GICS-beta1m (beta1m)</v>
+      </c>
+      <c r="F30" t="s">
+        <v>130</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s">
         <v>26</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2649,16 +2658,13 @@
         <v>0.1</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>4</v>
       </c>
-      <c r="P30" t="s">
-        <v>132</v>
-      </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="R30" t="s">
         <v>28</v>
@@ -2689,19 +2695,19 @@
       </c>
       <c r="E31" t="str">
         <f t="shared" si="5"/>
-        <v>30 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
+        <v>30 GICS-beta2m (beta2m)</v>
       </c>
       <c r="F31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="H31" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -2710,16 +2716,13 @@
         <v>0.1</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>4</v>
       </c>
-      <c r="P31" t="s">
-        <v>132</v>
-      </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="R31" t="s">
         <v>28</v>
@@ -2750,10 +2753,7 @@
       </c>
       <c r="E32" t="str">
         <f t="shared" si="5"/>
-        <v>31 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F32" t="s">
-        <v>141</v>
+        <v>31 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G32" t="s">
         <v>131</v>
@@ -2762,10 +2762,10 @@
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M32">
         <v>0.1</v>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="3:24" x14ac:dyDescent="0.25">
@@ -2811,7 +2811,10 @@
       </c>
       <c r="E33" t="str">
         <f t="shared" si="5"/>
-        <v>32 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>32 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F33" t="s">
+        <v>133</v>
       </c>
       <c r="G33" t="s">
         <v>131</v>
@@ -2820,7 +2823,7 @@
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -2869,7 +2872,10 @@
       </c>
       <c r="E34" t="str">
         <f t="shared" si="5"/>
-        <v>33 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
+        <v>33 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F34" t="s">
+        <v>141</v>
       </c>
       <c r="G34" t="s">
         <v>131</v>
@@ -2878,10 +2884,10 @@
         <v>26</v>
       </c>
       <c r="K34" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M34">
         <v>0.1</v>
@@ -2917,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="3:24" x14ac:dyDescent="0.25">
@@ -2927,7 +2933,7 @@
       </c>
       <c r="E35" t="str">
         <f t="shared" si="5"/>
-        <v>34 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
+        <v>34 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G35" t="s">
         <v>131</v>
@@ -2936,10 +2942,10 @@
         <v>26</v>
       </c>
       <c r="K35" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M35">
         <v>0.1</v>
@@ -2985,7 +2991,7 @@
       </c>
       <c r="E36" t="str">
         <f t="shared" si="5"/>
-        <v>35 GICS-rank (beta3m)</v>
+        <v>35 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G36" t="s">
         <v>131</v>
@@ -2994,10 +3000,10 @@
         <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M36">
         <v>0.1</v>
@@ -3008,6 +3014,9 @@
       <c r="O36">
         <v>4</v>
       </c>
+      <c r="P36" t="s">
+        <v>132</v>
+      </c>
       <c r="Q36" t="s">
         <v>27</v>
       </c>
@@ -3030,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="X36" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="3:24" x14ac:dyDescent="0.25">
@@ -3040,10 +3049,7 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" si="5"/>
-        <v>36 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
-      </c>
-      <c r="F37" t="s">
-        <v>141</v>
+        <v>36 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G37" t="s">
         <v>131</v>
@@ -3052,7 +3058,7 @@
         <v>26</v>
       </c>
       <c r="K37" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L37" t="s">
         <v>33</v>
@@ -3067,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="P37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
@@ -3091,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="3:24" x14ac:dyDescent="0.25">
@@ -3101,7 +3107,7 @@
       </c>
       <c r="E38" t="str">
         <f t="shared" si="5"/>
-        <v>37 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
+        <v>37 GICS-rank (beta3m)</v>
       </c>
       <c r="G38" t="s">
         <v>131</v>
@@ -3123,9 +3129,6 @@
       </c>
       <c r="O38">
         <v>4</v>
-      </c>
-      <c r="P38" t="s">
-        <v>137</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -3159,7 +3162,10 @@
       </c>
       <c r="E39" t="str">
         <f t="shared" si="5"/>
-        <v>38 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
+        <v>38 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
+      </c>
+      <c r="F39" t="s">
+        <v>141</v>
       </c>
       <c r="G39" t="s">
         <v>131</v>
@@ -3183,7 +3189,7 @@
         <v>4</v>
       </c>
       <c r="P39" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -3217,10 +3223,7 @@
       </c>
       <c r="E40" t="str">
         <f t="shared" si="5"/>
-        <v>39 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
-      </c>
-      <c r="F40" t="s">
-        <v>141</v>
+        <v>39 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
       </c>
       <c r="G40" t="s">
         <v>131</v>
@@ -3244,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="P40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -3278,10 +3281,7 @@
       </c>
       <c r="E41" t="str">
         <f t="shared" si="5"/>
-        <v>40 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
-      </c>
-      <c r="F41" t="s">
-        <v>141</v>
+        <v>40 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
       </c>
       <c r="G41" t="s">
         <v>131</v>
@@ -3305,7 +3305,7 @@
         <v>4</v>
       </c>
       <c r="P41" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
@@ -3339,7 +3339,10 @@
       </c>
       <c r="E42" t="str">
         <f t="shared" si="5"/>
-        <v>41 GICS-PdivMA20 (beta3m)</v>
+        <v>41 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
+      </c>
+      <c r="F42" t="s">
+        <v>141</v>
       </c>
       <c r="G42" t="s">
         <v>131</v>
@@ -3348,10 +3351,10 @@
         <v>26</v>
       </c>
       <c r="K42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L42" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M42">
         <v>0.1</v>
@@ -3362,6 +3365,9 @@
       <c r="O42">
         <v>4</v>
       </c>
+      <c r="P42" t="s">
+        <v>139</v>
+      </c>
       <c r="Q42" t="s">
         <v>27</v>
       </c>
@@ -3384,64 +3390,67 @@
         <v>0</v>
       </c>
       <c r="X42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="11">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C43">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="E43" s="11" t="str">
+      <c r="E43" t="str">
         <f t="shared" si="5"/>
-        <v>42 GICS-rank (beta3m)</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G43" s="11" t="s">
+        <v>42 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
+      </c>
+      <c r="F43" t="s">
+        <v>141</v>
+      </c>
+      <c r="G43" t="s">
         <v>131</v>
       </c>
-      <c r="H43" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" s="11" t="s">
+      <c r="H43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" t="s">
         <v>32</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="N43" s="11">
+      <c r="M43">
+        <v>0.1</v>
+      </c>
+      <c r="N43">
         <v>5</v>
       </c>
-      <c r="O43" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="R43" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="S43" s="11">
-        <v>1</v>
-      </c>
-      <c r="T43" s="11">
-        <v>3</v>
-      </c>
-      <c r="U43" s="11">
-        <v>0</v>
-      </c>
-      <c r="V43" s="11">
-        <v>20</v>
-      </c>
-      <c r="W43" s="11">
-        <v>0</v>
-      </c>
-      <c r="X43" s="11" t="s">
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" t="s">
+        <v>28</v>
+      </c>
+      <c r="S43">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>3</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>20</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3452,10 +3461,7 @@
       </c>
       <c r="E44" t="str">
         <f t="shared" si="5"/>
-        <v>43 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F44" t="s">
-        <v>130</v>
+        <v>43 GICS-PdivMA20 (beta3m)</v>
       </c>
       <c r="G44" t="s">
         <v>131</v>
@@ -3464,10 +3470,10 @@
         <v>26</v>
       </c>
       <c r="K44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M44">
         <v>0.1</v>
@@ -3478,11 +3484,8 @@
       <c r="O44">
         <v>4</v>
       </c>
-      <c r="P44" t="s">
-        <v>132</v>
-      </c>
       <c r="Q44" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R44" t="s">
         <v>28</v>
@@ -3506,62 +3509,62 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C45">
+    <row r="45" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="11">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E45" s="11" t="str">
         <f t="shared" si="5"/>
-        <v>44 GICS-rank (PdivMA20)</v>
-      </c>
-      <c r="F45" t="s">
-        <v>130</v>
-      </c>
-      <c r="G45" t="s">
+        <v>44 GICS-rank (beta3m)</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="H45" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" t="s">
+      <c r="H45" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="M45">
-        <v>0.1</v>
-      </c>
-      <c r="N45">
+      <c r="M45" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="N45" s="11">
         <v>5</v>
       </c>
-      <c r="O45">
-        <v>4</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>31</v>
-      </c>
-      <c r="R45" t="s">
-        <v>28</v>
-      </c>
-      <c r="S45">
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <v>3</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>20</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45" t="s">
-        <v>29</v>
+      <c r="O45" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="S45" s="11">
+        <v>1</v>
+      </c>
+      <c r="T45" s="11">
+        <v>3</v>
+      </c>
+      <c r="U45" s="11">
+        <v>0</v>
+      </c>
+      <c r="V45" s="11">
+        <v>20</v>
+      </c>
+      <c r="W45" s="11">
+        <v>0</v>
+      </c>
+      <c r="X45" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="3:24" x14ac:dyDescent="0.25">
@@ -3571,7 +3574,7 @@
       </c>
       <c r="E46" t="str">
         <f t="shared" si="5"/>
-        <v>45 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <v>45 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F46" t="s">
         <v>130</v>
@@ -3589,7 +3592,7 @@
         <v>33</v>
       </c>
       <c r="M46">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N46">
         <v>5</v>
@@ -3601,7 +3604,7 @@
         <v>132</v>
       </c>
       <c r="Q46" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R46" t="s">
         <v>28</v>
@@ -3632,7 +3635,7 @@
       </c>
       <c r="E47" t="str">
         <f t="shared" si="5"/>
-        <v>46 GICS-rank (beta3m)</v>
+        <v>46 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F47" t="s">
         <v>130</v>
@@ -3650,7 +3653,7 @@
         <v>33</v>
       </c>
       <c r="M47">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3659,7 +3662,7 @@
         <v>4</v>
       </c>
       <c r="Q47" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R47" t="s">
         <v>28</v>
@@ -3690,7 +3693,7 @@
       </c>
       <c r="E48" t="str">
         <f t="shared" si="5"/>
-        <v>47 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
+        <v>47 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F48" t="s">
         <v>130</v>
@@ -3708,10 +3711,10 @@
         <v>33</v>
       </c>
       <c r="M48">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O48">
         <v>4</v>
@@ -3720,7 +3723,7 @@
         <v>132</v>
       </c>
       <c r="Q48" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R48" t="s">
         <v>28</v>
@@ -3751,7 +3754,7 @@
       </c>
       <c r="E49" t="str">
         <f t="shared" si="5"/>
-        <v>48 GICS-rank (PdivMA20)</v>
+        <v>48 GICS-rank (beta3m)</v>
       </c>
       <c r="F49" t="s">
         <v>130</v>
@@ -3769,16 +3772,16 @@
         <v>33</v>
       </c>
       <c r="M49">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O49">
         <v>4</v>
       </c>
       <c r="Q49" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R49" t="s">
         <v>28</v>
@@ -3809,7 +3812,7 @@
       </c>
       <c r="E50" t="str">
         <f t="shared" si="5"/>
-        <v>49 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <v>49 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F50" t="s">
         <v>130</v>
@@ -3839,7 +3842,7 @@
         <v>132</v>
       </c>
       <c r="Q50" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R50" t="s">
         <v>28</v>
@@ -3870,7 +3873,7 @@
       </c>
       <c r="E51" t="str">
         <f t="shared" si="5"/>
-        <v>50 GICS-rank (beta3m)</v>
+        <v>50 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
@@ -3897,7 +3900,7 @@
         <v>4</v>
       </c>
       <c r="Q51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R51" t="s">
         <v>28</v>
@@ -3928,13 +3931,13 @@
       </c>
       <c r="E52" t="str">
         <f t="shared" si="5"/>
-        <v>51 GICS-rank (rsi)</v>
+        <v>51 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F52" t="s">
         <v>130</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="H52" t="s">
         <v>26</v>
@@ -3949,13 +3952,16 @@
         <v>0.1</v>
       </c>
       <c r="N52">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>4</v>
       </c>
+      <c r="P52" t="s">
+        <v>132</v>
+      </c>
       <c r="Q52" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="R52" t="s">
         <v>28</v>
@@ -3976,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="X52" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="3:24" x14ac:dyDescent="0.25">
@@ -3986,13 +3992,13 @@
       </c>
       <c r="E53" t="str">
         <f t="shared" si="5"/>
-        <v>52 GICS-rank (rank)</v>
+        <v>52 GICS-rank (beta3m)</v>
       </c>
       <c r="F53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="H53" t="s">
         <v>26</v>
@@ -4007,16 +4013,16 @@
         <v>0.1</v>
       </c>
       <c r="N53">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O53">
         <v>4</v>
       </c>
       <c r="Q53" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S53">
         <v>1</v>
@@ -4034,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="X53" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="3:24" x14ac:dyDescent="0.25">
@@ -4077,7 +4083,7 @@
         <v>28</v>
       </c>
       <c r="S54">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T54">
         <v>3</v>
@@ -4095,58 +4101,58 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="9">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C55">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="E55" s="9" t="str">
+      <c r="E55" t="str">
         <f t="shared" si="5"/>
         <v>54 GICS-rank (rank)</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" t="s">
         <v>134</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" t="s">
         <v>25</v>
       </c>
-      <c r="H55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" s="9" t="s">
+      <c r="H55" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" t="s">
         <v>32</v>
       </c>
-      <c r="L55" s="9" t="s">
+      <c r="L55" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N55" s="9">
+      <c r="M55">
+        <v>0.1</v>
+      </c>
+      <c r="N55">
         <v>10</v>
       </c>
-      <c r="O55" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q55" s="9" t="s">
+      <c r="O55">
+        <v>4</v>
+      </c>
+      <c r="Q55" t="s">
         <v>32</v>
       </c>
-      <c r="R55" s="9" t="s">
+      <c r="R55" t="s">
         <v>33</v>
       </c>
-      <c r="S55" s="9">
-        <v>-1</v>
-      </c>
-      <c r="T55" s="9">
-        <v>3</v>
-      </c>
-      <c r="U55" s="9">
-        <v>0</v>
-      </c>
-      <c r="V55" s="9">
-        <v>20</v>
-      </c>
-      <c r="W55" s="9">
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <v>3</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>20</v>
+      </c>
+      <c r="W55">
         <v>0</v>
       </c>
       <c r="X55" t="s">
@@ -4160,10 +4166,10 @@
       </c>
       <c r="E56" t="str">
         <f t="shared" si="5"/>
-        <v>55 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <v>55 GICS-rank (rsi)</v>
       </c>
       <c r="F56" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G56" t="s">
         <v>25</v>
@@ -4172,10 +4178,10 @@
         <v>26</v>
       </c>
       <c r="K56" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M56">
         <v>0.1</v>
@@ -4186,20 +4192,17 @@
       <c r="O56">
         <v>4</v>
       </c>
-      <c r="P56" t="s">
-        <v>143</v>
-      </c>
       <c r="Q56" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="R56" t="s">
         <v>28</v>
       </c>
       <c r="S56">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U56">
         <v>0</v>
@@ -4214,125 +4217,122 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C57">
+    <row r="57" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="9">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E57" s="9" t="str">
         <f t="shared" si="5"/>
-        <v>56 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F57" t="s">
-        <v>146</v>
-      </c>
-      <c r="G57" t="s">
+        <v>56 GICS-rank (rank)</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H57" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" t="s">
-        <v>28</v>
-      </c>
-      <c r="M57">
-        <v>0.1</v>
-      </c>
-      <c r="N57">
+      <c r="H57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M57" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N57" s="9">
         <v>10</v>
       </c>
-      <c r="O57">
-        <v>4</v>
-      </c>
-      <c r="P57" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>27</v>
-      </c>
-      <c r="R57" t="s">
-        <v>28</v>
-      </c>
-      <c r="S57">
-        <v>1</v>
-      </c>
-      <c r="T57">
-        <v>5</v>
-      </c>
-      <c r="U57">
-        <v>0</v>
-      </c>
-      <c r="V57">
-        <v>20</v>
-      </c>
-      <c r="W57">
+      <c r="O57" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R57" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S57" s="9">
+        <v>-1</v>
+      </c>
+      <c r="T57" s="9">
+        <v>3</v>
+      </c>
+      <c r="U57" s="9">
+        <v>0</v>
+      </c>
+      <c r="V57" s="9">
+        <v>20</v>
+      </c>
+      <c r="W57" s="9">
         <v>0</v>
       </c>
       <c r="X57" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="9">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C58">
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="E58" s="9" t="str">
+      <c r="E58" t="str">
         <f t="shared" si="5"/>
         <v>57 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" t="s">
         <v>146</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" t="s">
         <v>25</v>
       </c>
-      <c r="H58" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L58" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M58" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N58" s="9">
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58">
+        <v>0.1</v>
+      </c>
+      <c r="N58">
         <v>10</v>
       </c>
-      <c r="O58" s="9">
-        <v>4</v>
-      </c>
-      <c r="P58" s="9" t="s">
+      <c r="O58">
+        <v>4</v>
+      </c>
+      <c r="P58" t="s">
         <v>143</v>
       </c>
-      <c r="Q58" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R58" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S58" s="9">
-        <v>1</v>
-      </c>
-      <c r="T58" s="9">
-        <v>10</v>
-      </c>
-      <c r="U58" s="9">
-        <v>0</v>
-      </c>
-      <c r="V58" s="9">
-        <v>20</v>
-      </c>
-      <c r="W58" s="9">
-        <v>0</v>
-      </c>
-      <c r="X58" s="9" t="s">
+      <c r="Q58" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" t="s">
+        <v>28</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>20</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
         <v>58 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G59" t="s">
         <v>25</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="O59">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P59" t="s">
         <v>143</v>
@@ -4382,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U59">
         <v>0</v>
@@ -4397,125 +4397,125 @@
         <v>135</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C60">
+    <row r="60" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="9">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E60" s="9" t="str">
         <f t="shared" si="5"/>
         <v>59 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F60" t="s">
-        <v>147</v>
-      </c>
-      <c r="G60" t="s">
+      <c r="F60" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G60" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H60" t="s">
-        <v>26</v>
-      </c>
-      <c r="K60" t="s">
-        <v>27</v>
-      </c>
-      <c r="L60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M60">
-        <v>0.1</v>
-      </c>
-      <c r="N60">
+      <c r="H60" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N60" s="9">
         <v>10</v>
       </c>
-      <c r="O60">
-        <v>8</v>
-      </c>
-      <c r="P60" t="s">
+      <c r="O60" s="9">
+        <v>4</v>
+      </c>
+      <c r="P60" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Q60" t="s">
-        <v>27</v>
-      </c>
-      <c r="R60" t="s">
-        <v>28</v>
-      </c>
-      <c r="S60">
-        <v>1</v>
-      </c>
-      <c r="T60">
-        <v>3</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-      <c r="V60">
-        <v>20</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60" t="s">
+      <c r="Q60" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S60" s="9">
+        <v>1</v>
+      </c>
+      <c r="T60" s="9">
+        <v>10</v>
+      </c>
+      <c r="U60" s="9">
+        <v>0</v>
+      </c>
+      <c r="V60" s="9">
+        <v>20</v>
+      </c>
+      <c r="W60" s="9">
+        <v>0</v>
+      </c>
+      <c r="X60" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="61" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="9">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C61">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="E61" s="9" t="str">
+      <c r="E61" t="str">
         <f t="shared" si="5"/>
         <v>60 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" t="s">
         <v>147</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" t="s">
         <v>25</v>
       </c>
-      <c r="H61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M61" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N61" s="9">
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="K61" t="s">
+        <v>27</v>
+      </c>
+      <c r="L61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61">
+        <v>0.1</v>
+      </c>
+      <c r="N61">
         <v>10</v>
       </c>
-      <c r="O61" s="9">
-        <v>10</v>
-      </c>
-      <c r="P61" s="9" t="s">
+      <c r="O61">
+        <v>6</v>
+      </c>
+      <c r="P61" t="s">
         <v>143</v>
       </c>
-      <c r="Q61" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R61" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S61" s="9">
-        <v>1</v>
-      </c>
-      <c r="T61" s="9">
-        <v>3</v>
-      </c>
-      <c r="U61" s="9">
-        <v>0</v>
-      </c>
-      <c r="V61" s="9">
-        <v>20</v>
-      </c>
-      <c r="W61" s="9">
-        <v>0</v>
-      </c>
-      <c r="X61" s="9" t="s">
+      <c r="Q61" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" t="s">
+        <v>28</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <v>3</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>20</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4526,10 +4526,10 @@
       </c>
       <c r="E62" t="str">
         <f t="shared" si="5"/>
-        <v>61 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>61 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F62" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G62" t="s">
         <v>25</v>
@@ -4544,16 +4544,16 @@
         <v>28</v>
       </c>
       <c r="M62">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="N62">
         <v>10</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
@@ -4577,68 +4577,68 @@
         <v>0</v>
       </c>
       <c r="X62" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C63">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="9">
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E63" s="9" t="str">
         <f t="shared" si="5"/>
         <v>62 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F63" t="s">
-        <v>150</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="F63" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H63" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" t="s">
-        <v>27</v>
-      </c>
-      <c r="L63" t="s">
-        <v>28</v>
-      </c>
-      <c r="M63">
-        <v>0.15</v>
-      </c>
-      <c r="N63">
+      <c r="H63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N63" s="9">
         <v>10</v>
       </c>
-      <c r="O63">
-        <v>4</v>
-      </c>
-      <c r="P63" t="s">
+      <c r="O63" s="9">
+        <v>10</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Q63" t="s">
-        <v>27</v>
-      </c>
-      <c r="R63" t="s">
-        <v>28</v>
-      </c>
-      <c r="S63">
-        <v>1</v>
-      </c>
-      <c r="T63">
-        <v>3</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>20</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63" t="s">
-        <v>148</v>
+      <c r="Q63" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S63" s="9">
+        <v>1</v>
+      </c>
+      <c r="T63" s="9">
+        <v>3</v>
+      </c>
+      <c r="U63" s="9">
+        <v>0</v>
+      </c>
+      <c r="V63" s="9">
+        <v>20</v>
+      </c>
+      <c r="W63" s="9">
+        <v>0</v>
+      </c>
+      <c r="X63" s="9" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="3:24" x14ac:dyDescent="0.25">
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="U64">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="V64">
         <v>20</v>
@@ -4702,7 +4702,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C65">
         <f t="shared" si="3"/>
         <v>64</v>
@@ -4751,7 +4751,7 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="V65">
         <v>20</v>
@@ -4763,14 +4763,14 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C66">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="E66" t="str">
         <f t="shared" si="5"/>
-        <v>65 GICS-beta3m (beta3m)</v>
+        <v>65 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F66" t="s">
         <v>150</v>
@@ -4788,7 +4788,7 @@
         <v>28</v>
       </c>
       <c r="M66">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N66">
         <v>10</v>
@@ -4796,6 +4796,9 @@
       <c r="O66">
         <v>4</v>
       </c>
+      <c r="P66" t="s">
+        <v>132</v>
+      </c>
       <c r="Q66" t="s">
         <v>27</v>
       </c>
@@ -4809,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V66">
         <v>20</v>
@@ -4821,14 +4824,14 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C67">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
       <c r="E67" t="str">
         <f t="shared" si="5"/>
-        <v>66 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
+        <v>66 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F67" t="s">
         <v>150</v>
@@ -4846,7 +4849,7 @@
         <v>28</v>
       </c>
       <c r="M67">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N67">
         <v>10</v>
@@ -4855,7 +4858,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="Q67" t="s">
         <v>27</v>
@@ -4870,7 +4873,7 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V67">
         <v>20</v>
@@ -4882,81 +4885,75 @@
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="9">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C68">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="E68" s="9" t="str">
+      <c r="E68" t="str">
         <f t="shared" si="5"/>
-        <v>67 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F68" s="9" t="s">
+        <v>67 GICS-beta3m (beta3m)</v>
+      </c>
+      <c r="F68" t="s">
         <v>150</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" t="s">
         <v>25</v>
       </c>
-      <c r="H68" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M68" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N68" s="9">
+      <c r="H68" t="s">
+        <v>26</v>
+      </c>
+      <c r="K68" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" t="s">
+        <v>28</v>
+      </c>
+      <c r="M68">
+        <v>0.1</v>
+      </c>
+      <c r="N68">
         <v>10</v>
       </c>
-      <c r="O68" s="9">
-        <v>5</v>
-      </c>
-      <c r="P68" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q68" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R68" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S68" s="9">
-        <v>1</v>
-      </c>
-      <c r="T68" s="9">
-        <v>3</v>
-      </c>
-      <c r="U68" s="9">
-        <v>0</v>
-      </c>
-      <c r="V68" s="9">
-        <v>20</v>
-      </c>
-      <c r="W68" s="9">
-        <v>0</v>
-      </c>
-      <c r="X68" s="9" t="s">
+      <c r="O68">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" t="s">
+        <v>28</v>
+      </c>
+      <c r="S68">
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <v>3</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>20</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C69">
-        <f>C68+1</f>
+        <f t="shared" si="3"/>
         <v>68</v>
-      </c>
-      <c r="D69" t="s">
-        <v>153</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="5"/>
-        <v>68 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <v>68 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F69" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
@@ -4964,8 +4961,8 @@
       <c r="H69" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="12" t="s">
-        <v>129</v>
+      <c r="K69" t="s">
+        <v>27</v>
       </c>
       <c r="L69" t="s">
         <v>28</v>
@@ -4979,8 +4976,8 @@
       <c r="O69">
         <v>4</v>
       </c>
-      <c r="P69" s="12" t="s">
-        <v>143</v>
+      <c r="P69" t="s">
+        <v>149</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5004,74 +5001,71 @@
         <v>0</v>
       </c>
       <c r="X69" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="70" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C70">
-        <f>C69+1</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="9">
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="D70" t="s">
-        <v>153</v>
-      </c>
-      <c r="E70" t="str">
+      <c r="E70" s="9" t="str">
         <f t="shared" si="5"/>
-        <v>69 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F70" t="s">
-        <v>156</v>
-      </c>
-      <c r="G70" t="s">
+        <v>69 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G70" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H70" t="s">
-        <v>26</v>
-      </c>
-      <c r="K70" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="L70" t="s">
-        <v>28</v>
-      </c>
-      <c r="M70">
-        <v>0.1</v>
-      </c>
-      <c r="N70">
+      <c r="H70" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N70" s="9">
         <v>10</v>
       </c>
-      <c r="O70">
-        <v>4</v>
-      </c>
-      <c r="P70" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>27</v>
-      </c>
-      <c r="R70" t="s">
-        <v>28</v>
-      </c>
-      <c r="S70">
-        <v>1</v>
-      </c>
-      <c r="T70">
-        <v>3</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>20</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="71" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="O70" s="9">
+        <v>5</v>
+      </c>
+      <c r="P70" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q70" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S70" s="9">
+        <v>1</v>
+      </c>
+      <c r="T70" s="9">
+        <v>3</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0</v>
+      </c>
+      <c r="V70" s="9">
+        <v>20</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C71">
         <f>C70+1</f>
         <v>70</v>
@@ -5080,8 +5074,8 @@
         <v>153</v>
       </c>
       <c r="E71" t="str">
-        <f t="shared" ref="E71:E72" si="6">TEXT(C71,"00") &amp; " GICS-"&amp;K71&amp;" ("&amp;Q71&amp;IF(P71&lt;&gt;"","+ ","")&amp;P71&amp;")"</f>
-        <v>70 GICS-beta2m (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>70 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F71" t="s">
         <v>156</v>
@@ -5107,7 +5101,9 @@
       <c r="O71">
         <v>4</v>
       </c>
-      <c r="P71" s="12"/>
+      <c r="P71" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="Q71" t="s">
         <v>27</v>
       </c>
@@ -5133,7 +5129,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C72">
         <f>C71+1</f>
         <v>71</v>
@@ -5142,8 +5138,8 @@
         <v>153</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" si="6"/>
-        <v>71 GICS-beta1m (beta3m)</v>
+        <f t="shared" si="5"/>
+        <v>71 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F72" t="s">
         <v>156</v>
@@ -5169,7 +5165,9 @@
       <c r="O72">
         <v>4</v>
       </c>
-      <c r="P72" s="12"/>
+      <c r="P72" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="Q72" t="s">
         <v>27</v>
       </c>
@@ -5195,7 +5193,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="73" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C73">
         <f>C72+1</f>
         <v>72</v>
@@ -5204,7 +5202,7 @@
         <v>153</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" ref="E73" si="7">TEXT(C73,"00") &amp; " GICS-"&amp;K73&amp;" ("&amp;Q73&amp;IF(P73&lt;&gt;"","+ ","")&amp;P73&amp;")"</f>
+        <f t="shared" ref="E73:E74" si="6">TEXT(C73,"00") &amp; " GICS-"&amp;K73&amp;" ("&amp;Q73&amp;IF(P73&lt;&gt;"","+ ","")&amp;P73&amp;")"</f>
         <v>72 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F73" t="s">
@@ -5216,7 +5214,7 @@
       <c r="H73" t="s">
         <v>26</v>
       </c>
-      <c r="K73" t="s">
+      <c r="K73" s="12" t="s">
         <v>129</v>
       </c>
       <c r="L73" t="s">
@@ -5228,9 +5226,10 @@
       <c r="N73">
         <v>10</v>
       </c>
-      <c r="O73" s="12">
-        <v>5</v>
-      </c>
+      <c r="O73">
+        <v>4</v>
+      </c>
+      <c r="P73" s="12"/>
       <c r="Q73" t="s">
         <v>27</v>
       </c>
@@ -5256,20 +5255,20 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C74">
-        <f t="shared" ref="C74:C75" si="8">C73+1</f>
+        <f>C73+1</f>
         <v>73</v>
       </c>
       <c r="D74" t="s">
         <v>153</v>
       </c>
       <c r="E74" t="str">
-        <f t="shared" ref="E74:E75" si="9">TEXT(C74,"00") &amp; " GICS-"&amp;K74&amp;" ("&amp;Q74&amp;IF(P74&lt;&gt;"","+ ","")&amp;P74&amp;")"</f>
-        <v>73 GICS-beta2m (beta3m)</v>
+        <f t="shared" si="6"/>
+        <v>73 GICS-beta1m (beta3m)</v>
       </c>
       <c r="F74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -5277,8 +5276,8 @@
       <c r="H74" t="s">
         <v>26</v>
       </c>
-      <c r="K74" t="s">
-        <v>129</v>
+      <c r="K74" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="L74" t="s">
         <v>28</v>
@@ -5292,14 +5291,15 @@
       <c r="O74">
         <v>4</v>
       </c>
+      <c r="P74" s="12"/>
       <c r="Q74" t="s">
         <v>27</v>
       </c>
       <c r="R74" t="s">
         <v>28</v>
       </c>
-      <c r="S74" s="12">
-        <v>3</v>
+      <c r="S74">
+        <v>1</v>
       </c>
       <c r="T74">
         <v>3</v>
@@ -5317,64 +5317,427 @@
         <v>135</v>
       </c>
     </row>
-    <row r="75" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="9">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <f>C74+1</f>
+        <v>74</v>
+      </c>
+      <c r="D75" t="s">
+        <v>153</v>
+      </c>
+      <c r="E75" t="str">
+        <f t="shared" ref="E75" si="7">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
+        <v>74 GICS-beta2m (beta3m)</v>
+      </c>
+      <c r="F75" t="s">
+        <v>156</v>
+      </c>
+      <c r="G75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H75" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75" t="s">
+        <v>129</v>
+      </c>
+      <c r="L75" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75">
+        <v>0.1</v>
+      </c>
+      <c r="N75">
+        <v>10</v>
+      </c>
+      <c r="O75" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>27</v>
+      </c>
+      <c r="R75" t="s">
+        <v>28</v>
+      </c>
+      <c r="S75">
+        <v>1</v>
+      </c>
+      <c r="T75">
+        <v>3</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>20</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <f t="shared" ref="C76:C77" si="8">C75+1</f>
+        <v>75</v>
+      </c>
+      <c r="D76" t="s">
+        <v>153</v>
+      </c>
+      <c r="E76" t="str">
+        <f t="shared" ref="E76:E77" si="9">TEXT(C76,"00") &amp; " GICS-"&amp;K76&amp;" ("&amp;Q76&amp;IF(P76&lt;&gt;"","+ ","")&amp;P76&amp;")"</f>
+        <v>75 GICS-beta2m (beta3m)</v>
+      </c>
+      <c r="F76" t="s">
+        <v>155</v>
+      </c>
+      <c r="G76" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" t="s">
+        <v>26</v>
+      </c>
+      <c r="K76" t="s">
+        <v>129</v>
+      </c>
+      <c r="L76" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76">
+        <v>0.1</v>
+      </c>
+      <c r="N76">
+        <v>10</v>
+      </c>
+      <c r="O76">
+        <v>4</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" t="s">
+        <v>28</v>
+      </c>
+      <c r="S76" s="12">
+        <v>3</v>
+      </c>
+      <c r="T76">
+        <v>3</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>20</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C77" s="9">
         <f t="shared" si="8"/>
-        <v>74</v>
-      </c>
-      <c r="D75" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E75" s="9" t="str">
+      <c r="E77" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>74 GICS-beta2m (beta3m)</v>
-      </c>
-      <c r="F75" s="9" t="s">
+        <v>76 GICS-beta2m (beta3m)</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="G77" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K75" s="9" t="s">
+      <c r="H77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="L75" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N75" s="9">
+      <c r="L77" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N77" s="9">
         <v>10</v>
       </c>
-      <c r="O75" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q75" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R75" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S75" s="13" t="s">
+      <c r="O77" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q77" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S77" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="T75" s="9">
-        <v>3</v>
-      </c>
-      <c r="U75" s="9">
-        <v>0</v>
-      </c>
-      <c r="V75" s="9">
-        <v>20</v>
-      </c>
-      <c r="W75" s="9">
-        <v>0</v>
-      </c>
-      <c r="X75" s="9" t="s">
+      <c r="T77" s="9">
+        <v>3</v>
+      </c>
+      <c r="U77" s="9">
+        <v>0</v>
+      </c>
+      <c r="V77" s="9">
+        <v>20</v>
+      </c>
+      <c r="W77" s="9">
+        <v>0</v>
+      </c>
+      <c r="X77" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78">
+        <f>C77+1</f>
+        <v>77</v>
+      </c>
+      <c r="E78" t="str">
+        <f>TEXT(C78,"00") &amp; " Sector2-"&amp;K78&amp;" ("&amp;Q78&amp;IF(P78&lt;&gt;"","+ ","")&amp;P78&amp;")"</f>
+        <v>77 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F78" t="s">
+        <v>159</v>
+      </c>
+      <c r="G78" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" t="s">
+        <v>27</v>
+      </c>
+      <c r="L78" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78">
+        <v>0.1</v>
+      </c>
+      <c r="N78">
+        <v>10</v>
+      </c>
+      <c r="O78">
+        <v>4</v>
+      </c>
+      <c r="P78" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" t="s">
+        <v>28</v>
+      </c>
+      <c r="S78">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>3</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>20</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79">
+        <f>C78+1</f>
+        <v>78</v>
+      </c>
+      <c r="E79" t="str">
+        <f>TEXT(C79,"00") &amp; " Sector2-"&amp;K79&amp;" ("&amp;Q79&amp;IF(P79&lt;&gt;"","+ ","")&amp;P79&amp;")"</f>
+        <v>78 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="G79" t="s">
+        <v>158</v>
+      </c>
+      <c r="H79" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" t="s">
+        <v>45</v>
+      </c>
+      <c r="L79" t="s">
+        <v>28</v>
+      </c>
+      <c r="M79">
+        <v>0.1</v>
+      </c>
+      <c r="N79">
+        <v>10</v>
+      </c>
+      <c r="O79">
+        <v>4</v>
+      </c>
+      <c r="P79" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>27</v>
+      </c>
+      <c r="R79" t="s">
+        <v>28</v>
+      </c>
+      <c r="S79">
+        <v>1</v>
+      </c>
+      <c r="T79">
+        <v>3</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>20</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80">
+        <f>C79+1</f>
+        <v>79</v>
+      </c>
+      <c r="E80" t="str">
+        <f>TEXT(C80,"00") &amp; " Sector2-"&amp;K80&amp;" ("&amp;Q80&amp;IF(P80&lt;&gt;"","+ ","")&amp;P80&amp;")"</f>
+        <v>79 Sector2-beta3m (beta3m)</v>
+      </c>
+      <c r="G80" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" t="s">
+        <v>26</v>
+      </c>
+      <c r="K80" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" t="s">
+        <v>28</v>
+      </c>
+      <c r="M80">
+        <v>0.1</v>
+      </c>
+      <c r="N80">
+        <v>10</v>
+      </c>
+      <c r="O80">
+        <v>4</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>27</v>
+      </c>
+      <c r="R80" t="s">
+        <v>28</v>
+      </c>
+      <c r="S80">
+        <v>1</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>20</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81">
+        <f>C80+1</f>
+        <v>80</v>
+      </c>
+      <c r="E81" t="str">
+        <f>TEXT(C81,"00") &amp; " Sector2-"&amp;K81&amp;" ("&amp;Q81&amp;IF(P81&lt;&gt;"","+ ","")&amp;P81&amp;")"</f>
+        <v>80 Sector2-quot2050 (beta3m)</v>
+      </c>
+      <c r="G81" t="s">
+        <v>158</v>
+      </c>
+      <c r="H81" t="s">
+        <v>26</v>
+      </c>
+      <c r="K81" t="s">
+        <v>45</v>
+      </c>
+      <c r="L81" t="s">
+        <v>28</v>
+      </c>
+      <c r="M81">
+        <v>0.1</v>
+      </c>
+      <c r="N81">
+        <v>10</v>
+      </c>
+      <c r="O81">
+        <v>4</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R81" t="s">
+        <v>28</v>
+      </c>
+      <c r="S81">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>3</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>20</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81" t="s">
         <v>135</v>
       </c>
     </row>
